--- a/data/trending_integrated_20260910_10.xlsx
+++ b/data/trending_integrated_20260910_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5520</v>
+        <v>5250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+176.00%</t>
+          <t>+162.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -601,7 +601,7 @@
         <v>4000</v>
       </c>
       <c r="L2" t="n">
-        <v>5660</v>
+        <v>5700</v>
       </c>
       <c r="M2" t="n">
         <v>4000</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>428143236204</v>
+        <v>484080562239</v>
       </c>
       <c r="P2" t="n">
-        <v>5660</v>
+        <v>5700</v>
       </c>
       <c r="Q2" t="n">
         <v>4000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호, 합병 대상 업종(신재생에너지) 및 스팩주 특성 언급. 단기 변동성 속 종가 예측.</t>
+          <t>스팩주 특성상 변동성 언급. 합병 대상 업종 및 개미 꼬심 경계, 단타 및 도박성 매매 언급. 종가 예상치 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '신재생에너지']</t>
+          <t>['스팩주', '합병', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,70 +655,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28550</v>
+        <v>15240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+23.06%</t>
+          <t>+26.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="H3" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>23200</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>26900</v>
+        <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>30150</v>
+        <v>15250</v>
       </c>
       <c r="M3" t="n">
-        <v>24500</v>
+        <v>12720</v>
       </c>
       <c r="N3" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>26586377725</v>
+        <v>176288639405</v>
       </c>
       <c r="P3" t="n">
-        <v>34750</v>
+        <v>36200</v>
       </c>
       <c r="Q3" t="n">
-        <v>20450</v>
+        <v>8920</v>
       </c>
       <c r="R3" t="n">
-        <v>-37000</v>
+        <v>39000</v>
       </c>
       <c r="S3" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 소각 이슈와 연계된 기대감 부각. 30% 자사주 소각 뉴스 및 3연상 가능성 언급.</t>
+          <t>트럼프의 유가 상승 용인 및 호르무즈 해협 긴장 고조로 인한 유가 급등 전망. 단기 반등 초입 구간.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주소각', '이벤트', '식품']</t>
+          <t>['유가', '브렌트유', 'WTI']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14710</v>
+        <v>28800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.67%</t>
+          <t>+24.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>231</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>7.54</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12090</v>
+        <v>23200</v>
       </c>
       <c r="K4" t="n">
-        <v>12730</v>
+        <v>26900</v>
       </c>
       <c r="L4" t="n">
-        <v>15120</v>
+        <v>30150</v>
       </c>
       <c r="M4" t="n">
-        <v>12720</v>
+        <v>24500</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>160313043585</v>
+        <v>28473028000</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>34750</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>20450</v>
       </c>
       <c r="R4" t="n">
-        <v>39000</v>
+        <v>-37000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흥구석유, 유가 급등 요인(이란 사태, 트럼프 발언) 분석 및 급등 가능성 언급. 유가와 반도체 연관성 부인.</t>
+          <t>샘표식품 30% 자사주 소각 관련 뉴스 기반 상승. 샘표와의 관계 및 유동주식 수, 신한외인프매 관련 논의.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '이란', '트럼프']</t>
+          <t>['자사주 소각', '샘표', '유동주식']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3615</v>
+        <v>3645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.43%</t>
+          <t>+17.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>15181370606</v>
+        <v>16355378315</v>
       </c>
       <c r="P5" t="n">
         <v>20800</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>큰 폭의 상승 후 단기 과열 진입, 전고점 돌파 기대감과 함께 주가 조작 의혹 제기.</t>
+          <t>단기 과열 지정 속 윗꼬리 보합 마감. 전고점 돌파 시 6천원 목표.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['단기 과열', '전고점 돌파', '주가 조작']</t>
+          <t>['단기과열', '전고점', '테라뷰']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8170</v>
+        <v>1990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10.11%</t>
+          <t>+13.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>767</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7420</v>
+        <v>1760</v>
       </c>
       <c r="K6" t="n">
-        <v>8000</v>
+        <v>1782</v>
       </c>
       <c r="L6" t="n">
-        <v>9100</v>
+        <v>2020</v>
       </c>
       <c r="M6" t="n">
-        <v>7930</v>
+        <v>1772</v>
       </c>
       <c r="N6" t="n">
-        <v>0.77</v>
+        <v>2.07</v>
       </c>
       <c r="O6" t="n">
-        <v>48211805075</v>
+        <v>63200810901</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>4795</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>1524</v>
       </c>
       <c r="R6" t="n">
-        <v>100000</v>
+        <v>283000</v>
       </c>
       <c r="S6" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 세계 최초 항암제 내성 극복 기술 개발 성공 및 글로벌 제약사 참여 기대감. 5연상 전망.</t>
+          <t>외인 매수세 유입에도 불구하고 하락하며, 거래량 증가와 함께 일부 상승하는 모습. 신규 상장사 언급 및 석유 관련 테마 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['항암제내성', '오가노이드', '5연상']</t>
+          <t>['해운', '거래량', '외인']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3965</v>
+        <v>8230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+10.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.62</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>831</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3810</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
-        <v>3870</v>
+        <v>8000</v>
       </c>
       <c r="L7" t="n">
-        <v>4250</v>
+        <v>9100</v>
       </c>
       <c r="M7" t="n">
-        <v>3660</v>
+        <v>7930</v>
       </c>
       <c r="N7" t="n">
-        <v>3.19</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>96089823733</v>
+        <v>49939447000</v>
       </c>
       <c r="P7" t="n">
-        <v>8100</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>빛과전자, AI 데이터센터·6G 광통신 관련 뉴스 및 투기과열예방구간 회피 소식. 6G 기대감으로 인한 상승 전망.</t>
+          <t>세계 폐암학회 참여 및 항암제 내성 극복, FDA 2상 승인 기대감. 4연상 이상 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '6G', '광통신']</t>
+          <t>['폐암학회', '항암제', 'FDA']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>156200</v>
+        <v>3950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+3.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-1.62</v>
       </c>
       <c r="E8" t="n">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>611</v>
+        <v>122</v>
       </c>
       <c r="H8" t="n">
-        <v>15.65</v>
+        <v>1.57</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>153500</v>
+        <v>3810</v>
       </c>
       <c r="K8" t="n">
-        <v>155500</v>
+        <v>3870</v>
       </c>
       <c r="L8" t="n">
-        <v>164700</v>
+        <v>4250</v>
       </c>
       <c r="M8" t="n">
-        <v>154500</v>
+        <v>3660</v>
       </c>
       <c r="N8" t="n">
-        <v>15.25</v>
+        <v>3.19</v>
       </c>
       <c r="O8" t="n">
-        <v>213739865700</v>
+        <v>101050388174</v>
       </c>
       <c r="P8" t="n">
-        <v>164700</v>
+        <v>8100</v>
       </c>
       <c r="Q8" t="n">
-        <v>87700</v>
+        <v>592</v>
       </c>
       <c r="R8" t="n">
-        <v>112000</v>
+        <v>20000</v>
       </c>
       <c r="S8" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 폭등 및 정제마진 고공행진으로 인한 실적 개선 기대감. 단기 상승 후 조정 가능성도 제기.</t>
+          <t>AI 데이터센터·6G 광통신 사업 기대감 및 투기과열예고 회피. 15% 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가폭등', '정제마진', '실적개선']</t>
+          <t>['AI', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2115</v>
+        <v>154000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>270</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>115</v>
+        <v>642</v>
       </c>
       <c r="H9" t="n">
-        <v>0.85</v>
+        <v>15.65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2085</v>
+        <v>153500</v>
       </c>
       <c r="K9" t="n">
-        <v>2255</v>
+        <v>155500</v>
       </c>
       <c r="L9" t="n">
-        <v>2395</v>
+        <v>164700</v>
       </c>
       <c r="M9" t="n">
-        <v>2075</v>
+        <v>152500</v>
       </c>
       <c r="N9" t="n">
-        <v>0.51</v>
+        <v>15.25</v>
       </c>
       <c r="O9" t="n">
-        <v>13968491537</v>
+        <v>243767702200</v>
       </c>
       <c r="P9" t="n">
-        <v>2930</v>
+        <v>164700</v>
       </c>
       <c r="Q9" t="n">
-        <v>910</v>
+        <v>87700</v>
       </c>
       <c r="R9" t="n">
-        <v>-4000</v>
+        <v>112000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 시간외 단일가 거래량 및 외국인/기관 매수세 언급. 2000원 지지선 이탈 가능성 및 저항 구간 제시.</t>
+          <t>유가 상승에 따른 SK이노베이션 주가 상승 기대감. 정제마진 호조 및 환율 하락 영향 언급, 전고점 돌파 및 보유자 홀딩 의견.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['거래량', '저항', '매수']</t>
+          <t>['유가', '정제마진', '전고점']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1829000</v>
+        <v>2065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>796</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>463</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>1264</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>50.67</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1856000</v>
+        <v>2085</v>
       </c>
       <c r="K10" t="n">
-        <v>1879000</v>
+        <v>2255</v>
       </c>
       <c r="L10" t="n">
-        <v>1890000</v>
+        <v>2395</v>
       </c>
       <c r="M10" t="n">
-        <v>1825000</v>
+        <v>2050</v>
       </c>
       <c r="N10" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>1676519058000</v>
+        <v>14447934237</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>293000</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>-64000</v>
+        <v>-4000</v>
       </c>
       <c r="S10" t="n">
-        <v>-67000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 리밸런싱 물량 및 매도 폭탄 우려로 인한 하락세 전망. ADR 지표와 상반된 움직임 언급.</t>
+          <t>새만금 소식 관련 불확실성 및 2000원 이탈 가능성. 매물대 저항.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리밸런싱', 'ADR', '매도']</t>
+          <t>['새만금', '강동씨앤엘', '매물대']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265250</v>
+        <v>1820000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="G11" t="n">
-        <v>1469</v>
+        <v>1304</v>
       </c>
       <c r="H11" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="K11" t="n">
-        <v>269000</v>
+        <v>1879000</v>
       </c>
       <c r="L11" t="n">
-        <v>270500</v>
+        <v>1890000</v>
       </c>
       <c r="M11" t="n">
-        <v>264500</v>
+        <v>1820000</v>
       </c>
       <c r="N11" t="n">
-        <v>46.85</v>
+        <v>50.66</v>
       </c>
       <c r="O11" t="n">
-        <v>874314122000</v>
+        <v>1837173027000</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>71600</v>
+        <v>293000</v>
       </c>
       <c r="R11" t="n">
-        <v>236000</v>
+        <v>-64000</v>
       </c>
       <c r="S11" t="n">
-        <v>-272000</v>
+        <v>-67000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 하이닉스 대비 상대적 약세 및 자사주 매입 리스크 언급. 주가 부진에 대한 부정적 전망 제시.</t>
+          <t>SK하이닉스 주가 변동성 속 공매도 및 매도 압력 언급. 자사주 매입 및 소각, ADR 상승세, 옵션 만기 영향 분석.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주매입', '반도체', '주주환원']</t>
+          <t>['SK하이닉스', '공매도', '자사주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19000</v>
+        <v>264000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>790</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>465</v>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>1396</v>
       </c>
       <c r="H12" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19450</v>
+        <v>269500</v>
       </c>
       <c r="K12" t="n">
-        <v>18900</v>
+        <v>269000</v>
       </c>
       <c r="L12" t="n">
-        <v>19220</v>
+        <v>270500</v>
       </c>
       <c r="M12" t="n">
-        <v>18670</v>
+        <v>263500</v>
       </c>
       <c r="N12" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O12" t="n">
-        <v>38244989205</v>
+        <v>1009563716750</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>71600</v>
       </c>
       <c r="R12" t="n">
-        <v>58000</v>
+        <v>236000</v>
       </c>
       <c r="S12" t="n">
-        <v>-29000</v>
+        <v>-272000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대우건설, 미국 투자 및 원전 관련 긍정적 기대감 속 급등 가능성 언급. 일부는 하락 전망.</t>
+          <t>반도체 섹터 부진 속 삼성전자 주가 하락. 자사주 매입 및 주주 환원 요구, 하이닉스와의 비교 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미국투자', '원전', '급등']</t>
+          <t>['반도체', '주주환원', '자사주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14470</v>
+        <v>18750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.34</v>
+        <v>-0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>316</v>
+        <v>196</v>
       </c>
       <c r="H13" t="n">
-        <v>2.89</v>
+        <v>10.64</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14960</v>
+        <v>19450</v>
       </c>
       <c r="K13" t="n">
-        <v>15040</v>
+        <v>18900</v>
       </c>
       <c r="L13" t="n">
-        <v>15040</v>
+        <v>19220</v>
       </c>
       <c r="M13" t="n">
-        <v>14190</v>
+        <v>18670</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>58046710935</v>
+        <v>44192297955</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>1263</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-282000</v>
+        <v>58000</v>
       </c>
       <c r="S13" t="n">
-        <v>-7000</v>
+        <v>-29000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 테마 강세 속 상승 추세, 외인 순위 상승 및 거래량 증가로 16000원 돌파 기대.</t>
+          <t>대우건설 주가 상승 기대와 함께 조정 언급. 미국 투자 및 원전 관련 테마 언급, 자사주 소각 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신 테마', '외인 순위', '거래량 증가']</t>
+          <t>['건설', '미국 투자', '자사주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88500</v>
+        <v>14420</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>1.34</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>618</v>
+        <v>319</v>
       </c>
       <c r="H14" t="n">
-        <v>23.65</v>
+        <v>2.89</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>91700</v>
+        <v>14960</v>
       </c>
       <c r="K14" t="n">
-        <v>90000</v>
+        <v>15040</v>
       </c>
       <c r="L14" t="n">
-        <v>90700</v>
+        <v>15040</v>
       </c>
       <c r="M14" t="n">
-        <v>88400</v>
+        <v>14190</v>
       </c>
       <c r="N14" t="n">
-        <v>23.61</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>69570240900</v>
+        <v>60377302525</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>1263</v>
       </c>
       <c r="R14" t="n">
-        <v>-73000</v>
+        <v>-282000</v>
       </c>
       <c r="S14" t="n">
-        <v>-24000</v>
+        <v>-7000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 미국 원전 건설 '팀코리아' 참여 및 웨스턴하우스 지분 인수 건 등 역사적 호재 발생. 공매도 세력의 움직임과 관계없이 상승 추세 지속 전망.</t>
+          <t>미국 광통신 관련주 강세 및 AI 관련주 부각. 16000원 돌파 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전 건설', '웨스팅하우스', '호재']</t>
+          <t>['광통신', 'AI', '대한광통신']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13800</v>
+        <v>88200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="G15" t="n">
-        <v>234</v>
+        <v>623</v>
       </c>
       <c r="H15" t="n">
-        <v>6.09</v>
+        <v>23.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14320</v>
+        <v>91700</v>
       </c>
       <c r="K15" t="n">
-        <v>13800</v>
+        <v>90000</v>
       </c>
       <c r="L15" t="n">
-        <v>13900</v>
+        <v>90700</v>
       </c>
       <c r="M15" t="n">
-        <v>13260</v>
+        <v>87900</v>
       </c>
       <c r="N15" t="n">
-        <v>5.64</v>
+        <v>23.61</v>
       </c>
       <c r="O15" t="n">
-        <v>58719476755</v>
+        <v>85523580550</v>
       </c>
       <c r="P15" t="n">
-        <v>30200</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3540</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-70000</v>
+        <v>-73000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 금지에도 불구하고 하락 예상, 주포의 움직임에 따른 단기 매매 관점.</t>
+          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도 금지', '주포', '단기 매매']</t>
+          <t>['원전', '팀코리아', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12420</v>
+        <v>12440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-4.53%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H16" t="n">
         <v>0.14</v>
@@ -1898,7 +1898,7 @@
         <v>0.36</v>
       </c>
       <c r="O16" t="n">
-        <v>43722966995</v>
+        <v>46606545280</v>
       </c>
       <c r="P16" t="n">
         <v>20850</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재와 대규모 대미 투자 발표, 단기 하락에도 불구하고 추가 매수 및 추가 상승 전망.</t>
+          <t>3500억 달러 규모 대미 투자 호재와 원전 관련 불확실성 혼재. 20% 만족 후 일부 매도.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['최대 호재', '대미 투자', '추가 매수']</t>
+          <t>['대미투자', '호재', '삼미금속']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28750</v>
+        <v>13655</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.12%</t>
+          <t>-4.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>0.45</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33</v>
+        <v>6.09</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>30300</v>
+        <v>14320</v>
       </c>
       <c r="K17" t="n">
-        <v>30800</v>
+        <v>13800</v>
       </c>
       <c r="L17" t="n">
-        <v>31500</v>
+        <v>13900</v>
       </c>
       <c r="M17" t="n">
-        <v>28150</v>
+        <v>13260</v>
       </c>
       <c r="N17" t="n">
-        <v>0.31</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
-        <v>62602115200</v>
+        <v>61508785755</v>
       </c>
       <c r="P17" t="n">
-        <v>39350</v>
+        <v>30200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8200</v>
+        <v>3540</v>
       </c>
       <c r="R17" t="n">
-        <v>-1000</v>
+        <v>-70000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>급격한 하락 추세 속에서 반등 시도했으나 매수세 실종, 프로그램 매매에 의존한 단기 흐름에 대한 비관론.</t>
+          <t>공매도 금지 지정 속 하락 전망. 9시 20분까지 주포의 말아올림 시도.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['급격한 하락', '매수세 실종', '프로그램 매매']</t>
+          <t>['공매도', '우리기술', '주포']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14810</v>
+        <v>3650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15640</v>
+        <v>3865</v>
       </c>
       <c r="K18" t="n">
-        <v>15600</v>
+        <v>3845</v>
       </c>
       <c r="L18" t="n">
-        <v>15600</v>
+        <v>4075</v>
       </c>
       <c r="M18" t="n">
-        <v>14770</v>
+        <v>3650</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
-        <v>13906651730</v>
+        <v>38391092992</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>4335</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>1246</v>
       </c>
       <c r="R18" t="n">
-        <v>-14000</v>
+        <v>-73000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 설계 용역 발주 소식과 함께 건설 흑자 및 주가 회복 기대감 언급. 계단식 하락 후 반등 전망.</t>
+          <t>주간 조정 가능성 및 3500원대 하락 전망. 탈모 관련 신규 사업 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '건설', '설계용역']</t>
+          <t>['탈모', 'JW신약', '조정']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6460</v>
+        <v>14740</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>-5.75%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
         <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K19" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L19" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M19" t="n">
-        <v>6400</v>
+        <v>14740</v>
       </c>
       <c r="N19" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>6546717605</v>
+        <v>15077685360</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-131000</v>
+        <v>-14000</v>
       </c>
       <c r="S19" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스, 외국인 매도세와 함께 주가 부진 지속. 분사 및 로봇/반도체 사업 관련 투자 언급.</t>
+          <t>건설 및 반도체 관련 사업 언급. 호남 반도체 설계 용역 발주 및 2030년 반도체 인재 양성 언급, 주가 하락 및 횡보 구간.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['분사', '로봇', '반도체']</t>
+          <t>['건설', '반도체', '용역']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2100</v>
+        <v>6460</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.08%</t>
+          <t>-5.83%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.35</v>
+        <v>-1.03</v>
       </c>
       <c r="E20" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="H20" t="n">
-        <v>4.91</v>
+        <v>15.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2260</v>
+        <v>6860</v>
       </c>
       <c r="K20" t="n">
-        <v>2250</v>
+        <v>6800</v>
       </c>
       <c r="L20" t="n">
-        <v>2290</v>
+        <v>6820</v>
       </c>
       <c r="M20" t="n">
-        <v>2095</v>
+        <v>6400</v>
       </c>
       <c r="N20" t="n">
-        <v>5.26</v>
+        <v>16.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3586981194</v>
+        <v>6951061585</v>
       </c>
       <c r="P20" t="n">
-        <v>2705</v>
+        <v>13000</v>
       </c>
       <c r="Q20" t="n">
-        <v>1418</v>
+        <v>6030</v>
       </c>
       <c r="R20" t="n">
-        <v>-47000</v>
+        <v>-131000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>써니전자, 새로운 대주주 부각 및 M&amp;A 기대감으로 인한 단기 급등 가능성 언급. 1만원 목표가 제시.</t>
+          <t>분사 관련 논의 및 잡주 언급. 외국인 공매도에 대한 불만 제기, 한화 로보틱스 및 GPU 생산 관련 테마 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['M&amp;A', '대주주', '지분경쟁']</t>
+          <t>['분사', '공매도', '로보틱스']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,86 +2304,86 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>137</v>
+        <v>2115</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-44.76%</t>
+          <t>-6.42%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="E21" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="H21" t="n">
-        <v>5.86</v>
+        <v>4.91</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>248</v>
+        <v>2260</v>
       </c>
       <c r="K21" t="n">
-        <v>172</v>
+        <v>2250</v>
       </c>
       <c r="L21" t="n">
-        <v>172</v>
+        <v>2290</v>
       </c>
       <c r="M21" t="n">
-        <v>137</v>
+        <v>2080</v>
       </c>
       <c r="N21" t="n">
-        <v>6.18</v>
+        <v>5.26</v>
       </c>
       <c r="O21" t="n">
-        <v>409582898</v>
+        <v>3959605890</v>
       </c>
       <c r="P21" t="n">
-        <v>901</v>
+        <v>2705</v>
       </c>
       <c r="Q21" t="n">
-        <v>137</v>
+        <v>1418</v>
       </c>
       <c r="R21" t="n">
-        <v>29000</v>
+        <v>-47000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>정매 종목으로 분류, 거래량 부진 및 급락 가능성 언급, 상폐 우려 및 외국인 매매 패턴에 대한 부정적 시각.</t>
+          <t>M&amp;A 및 경영권 분쟁 관련 논의 활발. 새 최대주주 환영 및 지분 경쟁 관련 언급, 1만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['정매 종목', '거래량 부진', '상폐 우려']</t>
+          <t>['M&amp;A', '경영권', '지분']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2395,6 +2395,190 @@
         </is>
       </c>
       <c r="Z21" t="inlineStr">
+        <is>
+          <t>004770</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-7.59%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E22" t="n">
+        <v>107</v>
+      </c>
+      <c r="F22" t="n">
+        <v>63</v>
+      </c>
+      <c r="G22" t="n">
+        <v>176</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>30300</v>
+      </c>
+      <c r="K22" t="n">
+        <v>30800</v>
+      </c>
+      <c r="L22" t="n">
+        <v>31500</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27800</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O22" t="n">
+        <v>68843404575</v>
+      </c>
+      <c r="P22" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>보호예수 해제 물량과 누적 적자, 계단식 하락 추세를 근거로 하락 전망. 단, 외인/기관 물린 초보 투자자의 급등 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['보호예수', '누적적자', '계단식 하락']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>137</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-44.76%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E23" t="n">
+        <v>45</v>
+      </c>
+      <c r="F23" t="n">
+        <v>28</v>
+      </c>
+      <c r="G23" t="n">
+        <v>35</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>248</v>
+      </c>
+      <c r="K23" t="n">
+        <v>172</v>
+      </c>
+      <c r="L23" t="n">
+        <v>172</v>
+      </c>
+      <c r="M23" t="n">
+        <v>137</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O23" t="n">
+        <v>409582898</v>
+      </c>
+      <c r="P23" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>137</v>
+      </c>
+      <c r="R23" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>잦은 정매 종목 지정과 거래 정지 가능성을 언급하며 하락세 예상. 허매수와 외국인 매매 패턴에 대한 의구심 제기.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['정매종목', '거래정지', '허매수']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>008290</t>
         </is>

--- a/data/trending_integrated_20260910_10.xlsx
+++ b/data/trending_integrated_20260910_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5250</v>
+        <v>5160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+162.50%</t>
+          <t>+158.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>484080562239</v>
+        <v>504003157178</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스팩주 특성상 변동성 언급. 합병 대상 업종 및 개미 꼬심 경계, 단타 및 도박성 매매 언급. 종가 예상치 제시.</t>
+          <t>신재생에너지 관련 스팩주로, 단기 시세 차익 및 투자 주의 의견이 혼재함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '변동성']</t>
+          <t>['스팩주', '신재생에너지']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15240</v>
+        <v>15710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.05%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G3" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -693,7 +693,7 @@
         <v>12730</v>
       </c>
       <c r="L3" t="n">
-        <v>15250</v>
+        <v>15710</v>
       </c>
       <c r="M3" t="n">
         <v>12720</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>176288639405</v>
+        <v>220411763910</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>트럼프의 유가 상승 용인 및 호르무즈 해협 긴장 고조로 인한 유가 급등 전망. 단기 반등 초입 구간.</t>
+          <t>이란발 지정학적 리스크로 인한 유가 급등 수혜 기대감 및 시장 변동성 대응 전략이 논의됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가', '브렌트유', 'WTI']</t>
+          <t>['유가 급등', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28800</v>
+        <v>14800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+24.14%</t>
+          <t>+28.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>7.54</v>
+        <v>4.37</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23200</v>
+        <v>11550</v>
       </c>
       <c r="K4" t="n">
-        <v>26900</v>
+        <v>11780</v>
       </c>
       <c r="L4" t="n">
-        <v>30150</v>
+        <v>14830</v>
       </c>
       <c r="M4" t="n">
-        <v>24500</v>
+        <v>11700</v>
       </c>
       <c r="N4" t="n">
-        <v>7.58</v>
+        <v>4.63</v>
       </c>
       <c r="O4" t="n">
-        <v>28473028000</v>
+        <v>64436363755</v>
       </c>
       <c r="P4" t="n">
-        <v>34750</v>
+        <v>33575</v>
       </c>
       <c r="Q4" t="n">
-        <v>20450</v>
+        <v>9690</v>
       </c>
       <c r="R4" t="n">
-        <v>-37000</v>
+        <v>12000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>샘표식품 30% 자사주 소각 관련 뉴스 기반 상승. 샘표와의 관계 및 유동주식 수, 신한외인프매 관련 논의.</t>
+          <t>흥구석유와 키 맞추기 시세 분출 및 2연상 기대감 형성. 사우디 사태 관련 뉴스 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주 소각', '샘표', '유동주식']</t>
+          <t>['키맞추기', '2연상', '사우디']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,26 +832,26 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3645</v>
+        <v>28350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.39%</t>
+          <t>+22.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
         <v>49</v>
@@ -860,58 +860,58 @@
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3105</v>
+        <v>23200</v>
       </c>
       <c r="K5" t="n">
-        <v>3170</v>
+        <v>26900</v>
       </c>
       <c r="L5" t="n">
-        <v>3775</v>
+        <v>30150</v>
       </c>
       <c r="M5" t="n">
-        <v>3165</v>
+        <v>24500</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="O5" t="n">
-        <v>16355378315</v>
+        <v>29885541900</v>
       </c>
       <c r="P5" t="n">
-        <v>20800</v>
+        <v>34750</v>
       </c>
       <c r="Q5" t="n">
-        <v>1700</v>
+        <v>20450</v>
       </c>
       <c r="R5" t="n">
-        <v>16000</v>
+        <v>-37000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기 과열 지정 속 윗꼬리 보합 마감. 전고점 돌파 시 6천원 목표.</t>
+          <t>샘표의 자사주 소각 가능성과 연계된 샘표식품의 자사주 소각 기대감 고조. 30% 자사주 소각 단독 기사 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['단기과열', '전고점', '테라뷰']</t>
+          <t>['자사주 소각', '무상증자', '단독 기사']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1990</v>
+        <v>2140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.07%</t>
+          <t>+21.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
         <v>2.12</v>
@@ -969,7 +969,7 @@
         <v>1782</v>
       </c>
       <c r="L6" t="n">
-        <v>2020</v>
+        <v>2140</v>
       </c>
       <c r="M6" t="n">
         <v>1772</v>
@@ -978,7 +978,7 @@
         <v>2.07</v>
       </c>
       <c r="O6" t="n">
-        <v>63200810901</v>
+        <v>98506211378</v>
       </c>
       <c r="P6" t="n">
         <v>4795</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에도 불구하고 하락하며, 거래량 증가와 함께 일부 상승하는 모습. 신규 상장사 언급 및 석유 관련 테마 언급.</t>
+          <t>외인 매수세 유입 및 거래량 증가 기대 속 변동성 확대. 상폐 위기 STX 대비.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['해운', '거래량', '외인']</t>
+          <t>['외인', '거래량', '상폐']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8230</v>
+        <v>3665</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.92%</t>
+          <t>+18.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>831</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>3105</v>
       </c>
       <c r="K7" t="n">
-        <v>8000</v>
+        <v>3170</v>
       </c>
       <c r="L7" t="n">
-        <v>9100</v>
+        <v>3775</v>
       </c>
       <c r="M7" t="n">
-        <v>7930</v>
+        <v>3165</v>
       </c>
       <c r="N7" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>49939447000</v>
+        <v>16842629021</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>20800</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="R7" t="n">
-        <v>100000</v>
+        <v>16000</v>
       </c>
       <c r="S7" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세계 폐암학회 참여 및 항암제 내성 극복, FDA 2상 승인 기대감. 4연상 이상 목표.</t>
+          <t>단기 과열 지정 종목으로, 6천원 목표 및 5배 상승 가능성이 언급되나, 과열 및 주가 조작 의혹도 제기됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['폐암학회', '항암제', 'FDA']</t>
+          <t>['단기 과열', '주가 조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3950</v>
+        <v>8180</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>+10.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.62</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>122</v>
+        <v>904</v>
       </c>
       <c r="H8" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3810</v>
+        <v>7420</v>
       </c>
       <c r="K8" t="n">
-        <v>3870</v>
+        <v>8000</v>
       </c>
       <c r="L8" t="n">
-        <v>4250</v>
+        <v>9100</v>
       </c>
       <c r="M8" t="n">
-        <v>3660</v>
+        <v>7930</v>
       </c>
       <c r="N8" t="n">
-        <v>3.19</v>
+        <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>101050388174</v>
+        <v>52567494135</v>
       </c>
       <c r="P8" t="n">
-        <v>8100</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 데이터센터·6G 광통신 사업 기대감 및 투기과열예고 회피. 15% 상승 전망.</t>
+          <t>항암제 내성 극복 관련 기술을 보유한 바이오주로, 글로벌 제약사 참여 임상 및 FDA 2상 승인 기대감이 높음.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '6G', '광통신']</t>
+          <t>['항암제 내성', 'FDA 임상']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154000</v>
+        <v>3865</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>-1.62</v>
       </c>
       <c r="E9" t="n">
-        <v>270</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>642</v>
+        <v>131</v>
       </c>
       <c r="H9" t="n">
-        <v>15.65</v>
+        <v>1.57</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>153500</v>
+        <v>3810</v>
       </c>
       <c r="K9" t="n">
-        <v>155500</v>
+        <v>3870</v>
       </c>
       <c r="L9" t="n">
-        <v>164700</v>
+        <v>4250</v>
       </c>
       <c r="M9" t="n">
-        <v>152500</v>
+        <v>3660</v>
       </c>
       <c r="N9" t="n">
-        <v>15.25</v>
+        <v>3.19</v>
       </c>
       <c r="O9" t="n">
-        <v>243767702200</v>
+        <v>105990611104</v>
       </c>
       <c r="P9" t="n">
-        <v>164700</v>
+        <v>8100</v>
       </c>
       <c r="Q9" t="n">
-        <v>87700</v>
+        <v>592</v>
       </c>
       <c r="R9" t="n">
-        <v>112000</v>
+        <v>20000</v>
       </c>
       <c r="S9" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유가 상승에 따른 SK이노베이션 주가 상승 기대감. 정제마진 호조 및 환율 하락 영향 언급, 전고점 돌파 및 보유자 홀딩 의견.</t>
+          <t>AI 데이터센터 및 6G 광통신 관련주로, 투기 과열 지정 회피 및 15% 상승 전망을 제시함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', '전고점']</t>
+          <t>['AI 데이터센터', '6G 광통신']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2065</v>
+        <v>153700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="G10" t="n">
-        <v>118</v>
+        <v>655</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>15.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2085</v>
+        <v>153500</v>
       </c>
       <c r="K10" t="n">
-        <v>2255</v>
+        <v>155500</v>
       </c>
       <c r="L10" t="n">
-        <v>2395</v>
+        <v>164700</v>
       </c>
       <c r="M10" t="n">
-        <v>2050</v>
+        <v>152500</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51</v>
+        <v>15.25</v>
       </c>
       <c r="O10" t="n">
-        <v>14447934237</v>
+        <v>256335170000</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>164700</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>87700</v>
       </c>
       <c r="R10" t="n">
-        <v>-4000</v>
+        <v>112000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>새만금 소식 관련 불확실성 및 2000원 이탈 가능성. 매물대 저항.</t>
+          <t>유가 폭등 및 정제마진 상승 수혜 기대감. JP모건 대량 매수 패턴 관찰. 일부 단기 고점 경계.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['새만금', '강동씨앤엘', '매물대']</t>
+          <t>['유가', '정제마진', 'JP모건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1820000</v>
+        <v>2085</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>464</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>1304</v>
+        <v>129</v>
       </c>
       <c r="H11" t="n">
-        <v>50.67</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1856000</v>
+        <v>2085</v>
       </c>
       <c r="K11" t="n">
-        <v>1879000</v>
+        <v>2255</v>
       </c>
       <c r="L11" t="n">
-        <v>1890000</v>
+        <v>2395</v>
       </c>
       <c r="M11" t="n">
-        <v>1820000</v>
+        <v>2040</v>
       </c>
       <c r="N11" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>1837173027000</v>
+        <v>14937036419</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>293000</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>-64000</v>
+        <v>-4000</v>
       </c>
       <c r="S11" t="n">
-        <v>-67000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 변동성 속 공매도 및 매도 압력 언급. 자사주 매입 및 소각, ADR 상승세, 옵션 만기 영향 분석.</t>
+          <t>새만금 관련주로, 거래량 증가 및 2380~2515 저항 구간 언급 등 시세 차익 목적의 투자 심리가 관찰됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '공매도', '자사주']</t>
+          <t>['새만금', '거래량']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>264000</v>
+        <v>1816000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F12" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G12" t="n">
-        <v>1396</v>
+        <v>1299</v>
       </c>
       <c r="H12" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="K12" t="n">
-        <v>269000</v>
+        <v>1879000</v>
       </c>
       <c r="L12" t="n">
-        <v>270500</v>
+        <v>1890000</v>
       </c>
       <c r="M12" t="n">
-        <v>263500</v>
+        <v>1812000</v>
       </c>
       <c r="N12" t="n">
-        <v>46.85</v>
+        <v>50.66</v>
       </c>
       <c r="O12" t="n">
-        <v>1009563716750</v>
+        <v>2043222496000</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>71600</v>
+        <v>293000</v>
       </c>
       <c r="R12" t="n">
-        <v>236000</v>
+        <v>-64000</v>
       </c>
       <c r="S12" t="n">
-        <v>-272000</v>
+        <v>-67000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 섹터 부진 속 삼성전자 주가 하락. 자사주 매입 및 주주 환원 요구, 하이닉스와의 비교 언급.</t>
+          <t>대규모 자사주 소각에도 불구하고 단기 고점 경계 및 매물 출회. ADR 흐름 주목.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '주주환원', '자사주']</t>
+          <t>['자사주 소각', '단기 고점', 'ADR']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18750</v>
+        <v>263500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>790</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>466</v>
       </c>
       <c r="G13" t="n">
-        <v>196</v>
+        <v>1270</v>
       </c>
       <c r="H13" t="n">
-        <v>10.64</v>
+        <v>46.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19450</v>
+        <v>269500</v>
       </c>
       <c r="K13" t="n">
-        <v>18900</v>
+        <v>269000</v>
       </c>
       <c r="L13" t="n">
-        <v>19220</v>
+        <v>270500</v>
       </c>
       <c r="M13" t="n">
-        <v>18670</v>
+        <v>263500</v>
       </c>
       <c r="N13" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="O13" t="n">
-        <v>44192297955</v>
+        <v>1137012721750</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>71600</v>
       </c>
       <c r="R13" t="n">
-        <v>58000</v>
+        <v>236000</v>
       </c>
       <c r="S13" t="n">
-        <v>-29000</v>
+        <v>-272000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대우건설 주가 상승 기대와 함께 조정 언급. 미국 투자 및 원전 관련 테마 언급, 자사주 소각 요구.</t>
+          <t>외국인 매도세 지속 및 자사주 매입 리스크 언급. 반도체 업황 둔화 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['건설', '미국 투자', '자사주']</t>
+          <t>['외국인', '자사주', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14420</v>
+        <v>13780</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.61%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.34</v>
+        <v>0.45</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>319</v>
+        <v>256</v>
       </c>
       <c r="H14" t="n">
-        <v>2.89</v>
+        <v>6.09</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14960</v>
+        <v>14320</v>
       </c>
       <c r="K14" t="n">
-        <v>15040</v>
+        <v>13800</v>
       </c>
       <c r="L14" t="n">
-        <v>15040</v>
+        <v>13900</v>
       </c>
       <c r="M14" t="n">
-        <v>14190</v>
+        <v>13260</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>5.64</v>
       </c>
       <c r="O14" t="n">
-        <v>60377302525</v>
+        <v>64931170940</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>1263</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-282000</v>
+        <v>-70000</v>
       </c>
       <c r="S14" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주 강세 및 AI 관련주 부각. 16000원 돌파 및 상한가 기대.</t>
+          <t>신규 원전 건설 및 공매도 금지 관련 수혜 기대감이 있으나, 단기 하락 가능성 및 매도 의견도 공존함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '대한광통신']</t>
+          <t>['신규 원전', '공매도 금지']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88200</v>
+        <v>18710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>-3.80%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>623</v>
+        <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>91700</v>
+        <v>19450</v>
       </c>
       <c r="K15" t="n">
-        <v>90000</v>
+        <v>18900</v>
       </c>
       <c r="L15" t="n">
-        <v>90700</v>
+        <v>19220</v>
       </c>
       <c r="M15" t="n">
-        <v>87900</v>
+        <v>18670</v>
       </c>
       <c r="N15" t="n">
-        <v>23.61</v>
+        <v>10.85</v>
       </c>
       <c r="O15" t="n">
-        <v>85523580550</v>
+        <v>49672547410</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-73000</v>
+        <v>58000</v>
       </c>
       <c r="S15" t="n">
-        <v>-24000</v>
+        <v>-29000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
+          <t>중동발 악재에도 주가 영향 미미, 미국 투자 기대감 속 변동성 확대. 자사주 소각 요구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '팀코리아', '웨스팅하우스']</t>
+          <t>['중동', '미국 투자', '자사주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12440</v>
+        <v>87900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.53%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.22</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="G16" t="n">
-        <v>54</v>
+        <v>625</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>23.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13030</v>
+        <v>91700</v>
       </c>
       <c r="K16" t="n">
-        <v>13160</v>
+        <v>90000</v>
       </c>
       <c r="L16" t="n">
-        <v>13240</v>
+        <v>90700</v>
       </c>
       <c r="M16" t="n">
-        <v>12150</v>
+        <v>87800</v>
       </c>
       <c r="N16" t="n">
-        <v>0.36</v>
+        <v>23.61</v>
       </c>
       <c r="O16" t="n">
-        <v>46606545280</v>
+        <v>95170277500</v>
       </c>
       <c r="P16" t="n">
-        <v>20850</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>4020</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>231000</v>
+        <v>-73000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-24000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3500억 달러 규모 대미 투자 호재와 원전 관련 불확실성 혼재. 20% 만족 후 일부 매도.</t>
+          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대미투자', '호재', '삼미금속']</t>
+          <t>['원전', '팀코리아', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13655</v>
+        <v>14280</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.64%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.45</v>
+        <v>1.34</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>6.09</v>
+        <v>2.89</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14320</v>
+        <v>14960</v>
       </c>
       <c r="K17" t="n">
-        <v>13800</v>
+        <v>15040</v>
       </c>
       <c r="L17" t="n">
-        <v>13900</v>
+        <v>15040</v>
       </c>
       <c r="M17" t="n">
-        <v>13260</v>
+        <v>14190</v>
       </c>
       <c r="N17" t="n">
-        <v>5.64</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>61508785755</v>
+        <v>64451661340</v>
       </c>
       <c r="P17" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3540</v>
+        <v>1263</v>
       </c>
       <c r="R17" t="n">
-        <v>-70000</v>
+        <v>-282000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 금지 지정 속 하락 전망. 9시 20분까지 주포의 말아올림 시도.</t>
+          <t>미국 광통신 및 AI 관련주로, 16000원 돌파 및 5만 원까지 상승 전망이 제시되며, 외인 순매수세가 유입되고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '우리기술', '주포']</t>
+          <t>['광통신', 'AI 관련주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3650</v>
+        <v>14840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>-5.12%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="H18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3865</v>
+        <v>15640</v>
       </c>
       <c r="K18" t="n">
-        <v>3845</v>
+        <v>15600</v>
       </c>
       <c r="L18" t="n">
-        <v>4075</v>
+        <v>15600</v>
       </c>
       <c r="M18" t="n">
-        <v>3650</v>
+        <v>14700</v>
       </c>
       <c r="N18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>38391092992</v>
+        <v>16341367035</v>
       </c>
       <c r="P18" t="n">
-        <v>4335</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>1246</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>-73000</v>
+        <v>-14000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주간 조정 가능성 및 3500원대 하락 전망. 탈모 관련 신규 사업 기대감.</t>
+          <t>호남 반도체 설계 용역 발주 등 호재 뉴스 속 급등 기대감 형성. 건설 흑자 기록.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['탈모', 'JW신약', '조정']</t>
+          <t>['호남 반도체', '건설 흑자', '급등']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14740</v>
+        <v>12310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.75%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15640</v>
+        <v>13030</v>
       </c>
       <c r="K19" t="n">
-        <v>15600</v>
+        <v>13160</v>
       </c>
       <c r="L19" t="n">
-        <v>15600</v>
+        <v>13240</v>
       </c>
       <c r="M19" t="n">
-        <v>14740</v>
+        <v>12150</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="O19" t="n">
-        <v>15077685360</v>
+        <v>48316311855</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>20850</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>4020</v>
       </c>
       <c r="R19" t="n">
-        <v>-14000</v>
+        <v>231000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>건설 및 반도체 관련 사업 언급. 호남 반도체 설계 용역 발주 및 2030년 반도체 인재 양성 언급, 주가 하락 및 횡보 구간.</t>
+          <t>원전 및 방산 관련 대규모 투자 호재가 있으나, 투기 과열 지정 및 단기 하락 가능성이 언급되며 투자 심리가 엇갈림.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['건설', '반도체', '용역']</t>
+          <t>['원전', '방산 투자']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6460</v>
+        <v>6480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>-5.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-1.03</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
         <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="H20" t="n">
         <v>15.68</v>
@@ -2266,7 +2266,7 @@
         <v>16.71</v>
       </c>
       <c r="O20" t="n">
-        <v>6951061585</v>
+        <v>7475794505</v>
       </c>
       <c r="P20" t="n">
         <v>13000</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>분사 관련 논의 및 잡주 언급. 외국인 공매도에 대한 불만 제기, 한화 로보틱스 및 GPU 생산 관련 테마 언급.</t>
+          <t>외국인 매도세 지속 및 잡주 이미지 형성. 분사 및 경영진 교체 요구.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['분사', '공매도', '로보틱스']</t>
+          <t>['외국인', '분사', '경영진']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2115</v>
+        <v>3630</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-6.42%</t>
+          <t>-6.08%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H21" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K21" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L21" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M21" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N21" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O21" t="n">
-        <v>3959605890</v>
+        <v>39943801347</v>
       </c>
       <c r="P21" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q21" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R21" t="n">
-        <v>-47000</v>
+        <v>-73000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>M&amp;A 및 경영권 분쟁 관련 논의 활발. 새 최대주주 환영 및 지분 경쟁 관련 언급, 1만원 목표가 제시.</t>
+          <t>탈모 치료제 관련주로, 단기 조정 가능성 및 3500원 이하 매수 기회 언급이 있으나, 차트 붕괴 우려도 존재함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['M&amp;A', '경영권', '지분']</t>
+          <t>['탈모 치료제', '차트 붕괴']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28000</v>
+        <v>2110</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-7.59%</t>
+          <t>-6.64%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.02</v>
+        <v>-0.35</v>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c r="H22" t="n">
-        <v>0.33</v>
+        <v>4.91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>30300</v>
+        <v>2260</v>
       </c>
       <c r="K22" t="n">
-        <v>30800</v>
+        <v>2250</v>
       </c>
       <c r="L22" t="n">
-        <v>31500</v>
+        <v>2290</v>
       </c>
       <c r="M22" t="n">
-        <v>27800</v>
+        <v>2080</v>
       </c>
       <c r="N22" t="n">
-        <v>0.31</v>
+        <v>5.26</v>
       </c>
       <c r="O22" t="n">
-        <v>68843404575</v>
+        <v>4061332715</v>
       </c>
       <c r="P22" t="n">
-        <v>39350</v>
+        <v>2705</v>
       </c>
       <c r="Q22" t="n">
-        <v>8200</v>
+        <v>1418</v>
       </c>
       <c r="R22" t="n">
-        <v>-1000</v>
+        <v>-47000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량과 누적 적자, 계단식 하락 추세를 근거로 하락 전망. 단, 외인/기관 물린 초보 투자자의 급등 가능성 언급.</t>
+          <t>적대적 M&amp;A 가능성 및 지분 경쟁 부각, 신규 대주주 관련 기대감 형성. 변동성 확대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['보호예수', '누적적자', '계단식 하락']</t>
+          <t>['M&amp;A', '지분 경쟁', '대주주']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,26 +2488,26 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>137</v>
+        <v>28900</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-44.76%</t>
+          <t>-7.07%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.32</v>
+        <v>0.17</v>
       </c>
       <c r="E23" t="n">
         <v>45</v>
@@ -2516,58 +2516,58 @@
         <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="H23" t="n">
-        <v>5.86</v>
+        <v>12.31</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>248</v>
+        <v>31100</v>
       </c>
       <c r="K23" t="n">
-        <v>172</v>
+        <v>30450</v>
       </c>
       <c r="L23" t="n">
-        <v>172</v>
+        <v>30600</v>
       </c>
       <c r="M23" t="n">
-        <v>137</v>
+        <v>28800</v>
       </c>
       <c r="N23" t="n">
-        <v>6.18</v>
+        <v>12.14</v>
       </c>
       <c r="O23" t="n">
-        <v>409582898</v>
+        <v>37458793950</v>
       </c>
       <c r="P23" t="n">
-        <v>901</v>
+        <v>75900</v>
       </c>
       <c r="Q23" t="n">
-        <v>137</v>
+        <v>15000</v>
       </c>
       <c r="R23" t="n">
-        <v>29000</v>
+        <v>-198000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>잦은 정매 종목 지정과 거래 정지 가능성을 언급하며 하락세 예상. 허매수와 외국인 매매 패턴에 대한 의구심 제기.</t>
+          <t>상승 후 차익 실현 매물 출회 및 급락. 전고점 회복 기대감 약화. 구리 가격 상승 요인.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['정매종목', '거래정지', '허매수']</t>
+          <t>['차익 실현', '전고점', '구리']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2579,6 +2579,190 @@
         </is>
       </c>
       <c r="Z23" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>27800</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-8.25%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E24" t="n">
+        <v>120</v>
+      </c>
+      <c r="F24" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" t="n">
+        <v>182</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>30300</v>
+      </c>
+      <c r="K24" t="n">
+        <v>30800</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31500</v>
+      </c>
+      <c r="M24" t="n">
+        <v>27750</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O24" t="n">
+        <v>73804227950</v>
+      </c>
+      <c r="P24" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>누적 적자와 보호예수 해제 물량 부담 속 계단식 하락 전망. 프로그램 매매 외 매수세 부재로 하락세 지속 예상.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['누적적자', '보호예수', '계단식 하락']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>137</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-44.76%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E25" t="n">
+        <v>46</v>
+      </c>
+      <c r="F25" t="n">
+        <v>29</v>
+      </c>
+      <c r="G25" t="n">
+        <v>43</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>248</v>
+      </c>
+      <c r="K25" t="n">
+        <v>172</v>
+      </c>
+      <c r="L25" t="n">
+        <v>172</v>
+      </c>
+      <c r="M25" t="n">
+        <v>137</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O25" t="n">
+        <v>409582898</v>
+      </c>
+      <c r="P25" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>137</v>
+      </c>
+      <c r="R25" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>시가총액 미달 상폐 우려 속 거래 정지 가능성 제기. 허매수 유도로 인한 매도 압력 및 외국인 매매 차익 실현 관측.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>['시총미달', '상폐', '허매수']</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>008290</t>
         </is>

--- a/data/trending_integrated_20260910_10.xlsx
+++ b/data/trending_integrated_20260910_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5160</v>
+        <v>5080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+158.00%</t>
+          <t>+154.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G2" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>504003157178</v>
+        <v>512072155908</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신재생에너지 관련 스팩주로, 단기 시세 차익 및 투자 주의 의견이 혼재함.</t>
+          <t>NH스팩34호 합병 대상 신재생에너지 관련 기대감. 장 안좋을 때 수급 쏠림.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생에너지']</t>
+          <t>['스팩주', '신재생에너지', '합병']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="F3" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="H3" t="n">
         <v>0.03</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>220411763910</v>
+        <v>223127221700</v>
       </c>
       <c r="P3" t="n">
         <v>36200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크로 인한 유가 급등 수혜 기대감 및 시장 변동성 대응 전략이 논의됨.</t>
+          <t>흥구석유 유가 급등 수혜 기대. 이란 사태 및 지정학적 리스크 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가 급등', '지정학적 리스크']</t>
+          <t>['유가', '지정학적 리스크', '이란']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,10 +762,10 @@
         <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
         <v>17</v>
@@ -785,7 +785,7 @@
         <v>11780</v>
       </c>
       <c r="L4" t="n">
-        <v>14830</v>
+        <v>14880</v>
       </c>
       <c r="M4" t="n">
         <v>11700</v>
@@ -794,7 +794,7 @@
         <v>4.63</v>
       </c>
       <c r="O4" t="n">
-        <v>64436363755</v>
+        <v>71969624700</v>
       </c>
       <c r="P4" t="n">
         <v>33575</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 시세 분출 및 2연상 기대감 형성. 사우디 사태 관련 뉴스 부각.</t>
+          <t>흥구석유와 키 맞추기 시세 분출. 뉴스 기반 단기 급등 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['키맞추기', '2연상', '사우디']</t>
+          <t>['키 맞추기', '뉴스', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28350</v>
+        <v>28750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.20%</t>
+          <t>+23.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
         <v>7.54</v>
@@ -886,7 +886,7 @@
         <v>7.58</v>
       </c>
       <c r="O5" t="n">
-        <v>29885541900</v>
+        <v>32059977700</v>
       </c>
       <c r="P5" t="n">
         <v>34750</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>샘표의 자사주 소각 가능성과 연계된 샘표식품의 자사주 소각 기대감 고조. 30% 자사주 소각 단독 기사 확인.</t>
+          <t>샘표의 자사주 소각 가능성과 샘표식품과의 주주환원 정책 연계 기대감. 유동주식 대비 거래량 및 소각 필요성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 소각', '무상증자', '단독 기사']</t>
+          <t>['자사주 소각', '주주환원', 'PBR']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2140</v>
+        <v>2155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+21.59%</t>
+          <t>+22.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
         <v>2.12</v>
@@ -969,7 +969,7 @@
         <v>1782</v>
       </c>
       <c r="L6" t="n">
-        <v>2140</v>
+        <v>2175</v>
       </c>
       <c r="M6" t="n">
         <v>1772</v>
@@ -978,7 +978,7 @@
         <v>2.07</v>
       </c>
       <c r="O6" t="n">
-        <v>98506211378</v>
+        <v>119132420509</v>
       </c>
       <c r="P6" t="n">
         <v>4795</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 및 거래량 증가 기대 속 변동성 확대. 상폐 위기 STX 대비.</t>
+          <t>외인 매수세 유입 속 시세 형성 기대감. 단기 거래대금 증가 및 주가 상승.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인', '거래량', '상폐']</t>
+          <t>['외인', '시세', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3665</v>
+        <v>3510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.04%</t>
+          <t>+13.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
         <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>16842629021</v>
+        <v>17614968186</v>
       </c>
       <c r="P7" t="n">
         <v>20800</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 과열 지정 종목으로, 6천원 목표 및 5배 상승 가능성이 언급되나, 과열 및 주가 조작 의혹도 제기됨.</t>
+          <t>강한 수급 기반 상승세. 6천원 목표가 제시 및 단기 과열 구간 진입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기 과열', '주가 조작']</t>
+          <t>['수급', '목표가', '단기과열']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8180</v>
+        <v>8250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.24%</t>
+          <t>+11.19%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="H8" t="n">
         <v>1.17</v>
@@ -1162,7 +1162,7 @@
         <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>52567494135</v>
+        <v>53292465300</v>
       </c>
       <c r="P8" t="n">
         <v>21500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>항암제 내성 극복 관련 기술을 보유한 바이오주로, 글로벌 제약사 참여 임상 및 FDA 2상 승인 기대감이 높음.</t>
+          <t>세계 폐암학회 참여 및 항암제 내성 극복 기술 기반 급등 기대. FDA 임상 2상 결과 및 기술 이전 주목.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['항암제 내성', 'FDA 임상']</t>
+          <t>['폐암학회', '항암제', 'FDA']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3865</v>
+        <v>3930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+3.15%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-1.62</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>131</v>
@@ -1254,7 +1254,7 @@
         <v>3.19</v>
       </c>
       <c r="O9" t="n">
-        <v>105990611104</v>
+        <v>109964602175</v>
       </c>
       <c r="P9" t="n">
         <v>8100</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 데이터센터 및 6G 광통신 관련주로, 투기 과열 지정 회피 및 15% 상승 전망을 제시함.</t>
+          <t>빛과전자 투기과열종목 회피 및 통신 관련 기술 기대감. 장기전 대비.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '6G 광통신']</t>
+          <t>['투기과열', '통신', '장기전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153700</v>
+        <v>2125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>655</v>
+        <v>140</v>
       </c>
       <c r="H10" t="n">
-        <v>15.65</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>153500</v>
+        <v>2085</v>
       </c>
       <c r="K10" t="n">
-        <v>155500</v>
+        <v>2255</v>
       </c>
       <c r="L10" t="n">
-        <v>164700</v>
+        <v>2395</v>
       </c>
       <c r="M10" t="n">
-        <v>152500</v>
+        <v>2040</v>
       </c>
       <c r="N10" t="n">
-        <v>15.25</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>256335170000</v>
+        <v>15410717850</v>
       </c>
       <c r="P10" t="n">
-        <v>164700</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>87700</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>112000</v>
+        <v>-4000</v>
       </c>
       <c r="S10" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제마진 상승 수혜 기대감. JP모건 대량 매수 패턴 관찰. 일부 단기 고점 경계.</t>
+          <t>새만금 소식 기반 긍정적 움직임. 외인 매수세 관찰 및 저항 구간 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', 'JP모건']</t>
+          <t>['새만금', '외인', '저항']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2085</v>
+        <v>153600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="G11" t="n">
-        <v>129</v>
+        <v>690</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>15.65</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2085</v>
+        <v>153500</v>
       </c>
       <c r="K11" t="n">
-        <v>2255</v>
+        <v>155500</v>
       </c>
       <c r="L11" t="n">
-        <v>2395</v>
+        <v>164700</v>
       </c>
       <c r="M11" t="n">
-        <v>2040</v>
+        <v>152500</v>
       </c>
       <c r="N11" t="n">
-        <v>0.51</v>
+        <v>15.25</v>
       </c>
       <c r="O11" t="n">
-        <v>14937036419</v>
+        <v>264886249900</v>
       </c>
       <c r="P11" t="n">
-        <v>2930</v>
+        <v>164700</v>
       </c>
       <c r="Q11" t="n">
-        <v>910</v>
+        <v>87700</v>
       </c>
       <c r="R11" t="n">
-        <v>-4000</v>
+        <v>112000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>새만금 관련주로, 거래량 증가 및 2380~2515 저항 구간 언급 등 시세 차익 목적의 투자 심리가 관찰됨.</t>
+          <t>SK이노베이션 유가 급등 수혜 기대. 재무 개선 및 주주 이익 증대 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['새만금', '거래량']</t>
+          <t>['유가', '정제마진', '재무 개선']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1816000</v>
+        <v>264250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F12" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="G12" t="n">
-        <v>1299</v>
+        <v>1251</v>
       </c>
       <c r="H12" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1856000</v>
+        <v>269500</v>
       </c>
       <c r="K12" t="n">
-        <v>1879000</v>
+        <v>269000</v>
       </c>
       <c r="L12" t="n">
-        <v>1890000</v>
+        <v>270500</v>
       </c>
       <c r="M12" t="n">
-        <v>1812000</v>
+        <v>263500</v>
       </c>
       <c r="N12" t="n">
-        <v>50.66</v>
+        <v>46.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2043222496000</v>
+        <v>1212617634500</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>293000</v>
+        <v>71600</v>
       </c>
       <c r="R12" t="n">
-        <v>-64000</v>
+        <v>236000</v>
       </c>
       <c r="S12" t="n">
-        <v>-67000</v>
+        <v>-272000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대규모 자사주 소각에도 불구하고 단기 고점 경계 및 매물 출회. ADR 흐름 주목.</t>
+          <t>삼성전자 주가 하락에 대한 부정적 전망. 외인 매도 및 악재 요인 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 소각', '단기 고점', 'ADR']</t>
+          <t>['악재', '외인 매도', '반도체']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>263500</v>
+        <v>1816000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F13" t="n">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="G13" t="n">
-        <v>1270</v>
+        <v>1306</v>
       </c>
       <c r="H13" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="K13" t="n">
-        <v>269000</v>
+        <v>1879000</v>
       </c>
       <c r="L13" t="n">
-        <v>270500</v>
+        <v>1890000</v>
       </c>
       <c r="M13" t="n">
-        <v>263500</v>
+        <v>1811000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.85</v>
+        <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1137012721750</v>
+        <v>2166983396000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>71600</v>
+        <v>293000</v>
       </c>
       <c r="R13" t="n">
-        <v>236000</v>
+        <v>-64000</v>
       </c>
       <c r="S13" t="n">
-        <v>-272000</v>
+        <v>-67000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 자사주 매입 리스크 언급. 반도체 업황 둔화 우려.</t>
+          <t>대규모 자사주 소각 예정. ADR 괴리율 및 마녀의 날 변동성 고려, 매수 기회 관점.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인', '자사주', '반도체']</t>
+          <t>['자사주소각', 'ADR', '마녀의날']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13780</v>
+        <v>18790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.45</v>
+        <v>-0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="H14" t="n">
-        <v>6.09</v>
+        <v>10.64</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14320</v>
+        <v>19450</v>
       </c>
       <c r="K14" t="n">
-        <v>13800</v>
+        <v>18900</v>
       </c>
       <c r="L14" t="n">
-        <v>13900</v>
+        <v>19220</v>
       </c>
       <c r="M14" t="n">
-        <v>13260</v>
+        <v>18670</v>
       </c>
       <c r="N14" t="n">
-        <v>5.64</v>
+        <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>64931170940</v>
+        <v>51867278060</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-70000</v>
+        <v>58000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신규 원전 건설 및 공매도 금지 관련 수혜 기대감이 있으나, 단기 하락 가능성 및 매도 의견도 공존함.</t>
+          <t>대우건설 주가 하락 및 불확실성. 중동전쟁 영향 미미 속 단기 반등 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신규 원전', '공매도 금지']</t>
+          <t>['대우건설', '주가', '중동전쟁']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18710</v>
+        <v>13820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.80%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.21</v>
+        <v>0.45</v>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="H15" t="n">
-        <v>10.64</v>
+        <v>6.09</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19450</v>
+        <v>14320</v>
       </c>
       <c r="K15" t="n">
-        <v>18900</v>
+        <v>13800</v>
       </c>
       <c r="L15" t="n">
-        <v>19220</v>
+        <v>13900</v>
       </c>
       <c r="M15" t="n">
-        <v>18670</v>
+        <v>13260</v>
       </c>
       <c r="N15" t="n">
-        <v>10.85</v>
+        <v>5.64</v>
       </c>
       <c r="O15" t="n">
-        <v>49672547410</v>
+        <v>67397865850</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R15" t="n">
-        <v>58000</v>
+        <v>-70000</v>
       </c>
       <c r="S15" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>중동발 악재에도 주가 영향 미미, 미국 투자 기대감 속 변동성 확대. 자사주 소각 요구.</t>
+          <t>미국 신규 원전 건설 소식 기반 상승 기대. 공매도 금지 지정 및 단기 조정 예상.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['중동', '미국 투자', '자사주']</t>
+          <t>['원전', '공매도', '조정']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87900</v>
+        <v>29200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>625</v>
+        <v>209</v>
       </c>
       <c r="H16" t="n">
-        <v>23.65</v>
+        <v>0.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>91700</v>
+        <v>30300</v>
       </c>
       <c r="K16" t="n">
-        <v>90000</v>
+        <v>30800</v>
       </c>
       <c r="L16" t="n">
-        <v>90700</v>
+        <v>31500</v>
       </c>
       <c r="M16" t="n">
-        <v>87800</v>
+        <v>27750</v>
       </c>
       <c r="N16" t="n">
-        <v>23.61</v>
+        <v>0.31</v>
       </c>
       <c r="O16" t="n">
-        <v>95170277500</v>
+        <v>88597288325</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>39350</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R16" t="n">
-        <v>-73000</v>
+        <v>-1000</v>
       </c>
       <c r="S16" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
+          <t>하락 추세 지속 및 매수세 실종으로 인한 부정적 전망. 축제는 끝났다는 의견. 단기적인 희망 회로를 경계.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '팀코리아', '웨스팅하우스']</t>
+          <t>['계단식 하락', '매수세 실종', '신규주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14280</v>
+        <v>88100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.34</v>
+        <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>321</v>
+        <v>644</v>
       </c>
       <c r="H17" t="n">
-        <v>2.89</v>
+        <v>23.65</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14960</v>
+        <v>91700</v>
       </c>
       <c r="K17" t="n">
-        <v>15040</v>
+        <v>90000</v>
       </c>
       <c r="L17" t="n">
-        <v>15040</v>
+        <v>90700</v>
       </c>
       <c r="M17" t="n">
-        <v>14190</v>
+        <v>87800</v>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>23.61</v>
       </c>
       <c r="O17" t="n">
-        <v>64451661340</v>
+        <v>100434741100</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>1263</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-282000</v>
+        <v>-73000</v>
       </c>
       <c r="S17" t="n">
-        <v>-7000</v>
+        <v>-24000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신 및 AI 관련주로, 16000원 돌파 및 5만 원까지 상승 전망이 제시되며, 외인 순매수세가 유입되고 있음.</t>
+          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 관련주']</t>
+          <t>['원전', '팀코리아', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14840</v>
+        <v>14320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-5.12%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15640</v>
+        <v>14960</v>
       </c>
       <c r="K18" t="n">
-        <v>15600</v>
+        <v>15040</v>
       </c>
       <c r="L18" t="n">
-        <v>15600</v>
+        <v>15040</v>
       </c>
       <c r="M18" t="n">
-        <v>14700</v>
+        <v>14190</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>16341367035</v>
+        <v>66636849750</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>1263</v>
       </c>
       <c r="R18" t="n">
-        <v>-14000</v>
+        <v>-282000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>호남 반도체 설계 용역 발주 등 호재 뉴스 속 급등 기대감 형성. 건설 흑자 기록.</t>
+          <t>미국 광통신 강세 및 AI 관련주 비교. 16000원 돌파 목표 및 시간 외 거래량 주목.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남 반도체', '건설 흑자', '급등']</t>
+          <t>['광통신', 'AI', '시간외거래']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12310</v>
+        <v>6560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.22</v>
+        <v>-1.03</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>15.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13030</v>
+        <v>6860</v>
       </c>
       <c r="K19" t="n">
-        <v>13160</v>
+        <v>6800</v>
       </c>
       <c r="L19" t="n">
-        <v>13240</v>
+        <v>6820</v>
       </c>
       <c r="M19" t="n">
-        <v>12150</v>
+        <v>6400</v>
       </c>
       <c r="N19" t="n">
-        <v>0.36</v>
+        <v>16.71</v>
       </c>
       <c r="O19" t="n">
-        <v>48316311855</v>
+        <v>8046225795</v>
       </c>
       <c r="P19" t="n">
-        <v>20850</v>
+        <v>13000</v>
       </c>
       <c r="Q19" t="n">
-        <v>4020</v>
+        <v>6030</v>
       </c>
       <c r="R19" t="n">
-        <v>231000</v>
+        <v>-131000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 및 방산 관련 대규모 투자 호재가 있으나, 투기 과열 지정 및 단기 하락 가능성이 언급되며 투자 심리가 엇갈림.</t>
+          <t>외국인 매도세 지속 및 잡주 이미지 형성. 분사 및 경영진 교체 요구.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '방산 투자']</t>
+          <t>['외국인', '분사', '경영진']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,26 +2212,26 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6480</v>
+        <v>12370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.54%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.03</v>
+        <v>-0.22</v>
       </c>
       <c r="E20" t="n">
         <v>66</v>
@@ -2240,62 +2240,62 @@
         <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>174</v>
+        <v>57</v>
       </c>
       <c r="H20" t="n">
-        <v>15.68</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6860</v>
+        <v>13030</v>
       </c>
       <c r="K20" t="n">
-        <v>6800</v>
+        <v>13160</v>
       </c>
       <c r="L20" t="n">
-        <v>6820</v>
+        <v>13240</v>
       </c>
       <c r="M20" t="n">
-        <v>6400</v>
+        <v>12150</v>
       </c>
       <c r="N20" t="n">
-        <v>16.71</v>
+        <v>0.36</v>
       </c>
       <c r="O20" t="n">
-        <v>7475794505</v>
+        <v>49128063860</v>
       </c>
       <c r="P20" t="n">
-        <v>13000</v>
+        <v>20850</v>
       </c>
       <c r="Q20" t="n">
-        <v>6030</v>
+        <v>4020</v>
       </c>
       <c r="R20" t="n">
-        <v>-131000</v>
+        <v>231000</v>
       </c>
       <c r="S20" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 잡주 이미지 형성. 분사 및 경영진 교체 요구.</t>
+          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['외국인', '분사', '경영진']</t>
+          <t>['호재', '원전', '하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3630</v>
+        <v>14800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="H21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3865</v>
+        <v>15640</v>
       </c>
       <c r="K21" t="n">
-        <v>3845</v>
+        <v>15600</v>
       </c>
       <c r="L21" t="n">
-        <v>4075</v>
+        <v>15600</v>
       </c>
       <c r="M21" t="n">
-        <v>3605</v>
+        <v>14700</v>
       </c>
       <c r="N21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>39943801347</v>
+        <v>16794377895</v>
       </c>
       <c r="P21" t="n">
-        <v>4335</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>1246</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-73000</v>
+        <v>-14000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련주로, 단기 조정 가능성 및 3500원 이하 매수 기회 언급이 있으나, 차트 붕괴 우려도 존재함.</t>
+          <t>호남 반도체 설계 용역 발주 및 건설 흑자 기반 상승 기대. 14000원 목표가 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '차트 붕괴']</t>
+          <t>['반도체', '건설', '흑자']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2110</v>
+        <v>3620</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-6.64%</t>
+          <t>-6.34%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H22" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K22" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L22" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M22" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N22" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>4061332715</v>
+        <v>40602477592</v>
       </c>
       <c r="P22" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q22" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R22" t="n">
-        <v>-47000</v>
+        <v>-73000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>적대적 M&amp;A 가능성 및 지분 경쟁 부각, 신규 대주주 관련 기대감 형성. 변동성 확대.</t>
+          <t>주가 조정 예상 속 단기 매매 관점. 차트 분석 기반으로 방향성 제시.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['M&amp;A', '지분 경쟁', '대주주']</t>
+          <t>['차트', '매수', '단타']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28900</v>
+        <v>2115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-7.07%</t>
+          <t>-6.42%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="H23" t="n">
-        <v>12.31</v>
+        <v>4.91</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,47 +2527,47 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>31100</v>
+        <v>2260</v>
       </c>
       <c r="K23" t="n">
-        <v>30450</v>
+        <v>2250</v>
       </c>
       <c r="L23" t="n">
-        <v>30600</v>
+        <v>2290</v>
       </c>
       <c r="M23" t="n">
-        <v>28800</v>
+        <v>2080</v>
       </c>
       <c r="N23" t="n">
-        <v>12.14</v>
+        <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>37458793950</v>
+        <v>4102132365</v>
       </c>
       <c r="P23" t="n">
-        <v>75900</v>
+        <v>2705</v>
       </c>
       <c r="Q23" t="n">
-        <v>15000</v>
+        <v>1418</v>
       </c>
       <c r="R23" t="n">
-        <v>-198000</v>
+        <v>-47000</v>
       </c>
       <c r="S23" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>상승 후 차익 실현 매물 출회 및 급락. 전고점 회복 기대감 약화. 구리 가격 상승 요인.</t>
+          <t>써니전자 경영권 분쟁 및 M&amp;A 관련 기대감. 새로운 대주주 관련 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['차익 실현', '전고점', '구리']</t>
+          <t>['M&amp;A', '경영권', '대주주']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2580,77 +2580,77 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27800</v>
+        <v>28950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-8.25%</t>
+          <t>-6.91%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="H24" t="n">
-        <v>0.33</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>30300</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>30800</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>31500</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>27750</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>0.31</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>73804227950</v>
+        <v>38872418800</v>
       </c>
       <c r="P24" t="n">
-        <v>39350</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>8200</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
+        <v>-198000</v>
+      </c>
+      <c r="S24" t="n">
         <v>-1000</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>누적 적자와 보호예수 해제 물량 부담 속 계단식 하락 전망. 프로그램 매매 외 매수세 부재로 하락세 지속 예상.</t>
+          <t>대한전선 주가 변동성 확대. 상승분 반납 및 단기 하락세 우세.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['누적적자', '보호예수', '계단식 하락']</t>
+          <t>['변동성', '주가', '상승분 반납']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-44.76%</t>
+          <t>-41.94%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.32</v>
       </c>
       <c r="E25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H25" t="n">
         <v>5.86</v>
@@ -2726,7 +2726,7 @@
         <v>6.18</v>
       </c>
       <c r="O25" t="n">
-        <v>409582898</v>
+        <v>567452546</v>
       </c>
       <c r="P25" t="n">
         <v>901</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>시가총액 미달 상폐 우려 속 거래 정지 가능성 제기. 허매수 유도로 인한 매도 압력 및 외국인 매매 차익 실현 관측.</t>
+          <t>시가총액 미달 상폐 우려 속 급락. 허매수/허매도 관찰 및 거래 정지 가능성 제기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['시총미달', '상폐', '허매수']</t>
+          <t>['상폐', '시가총액', '거래정지']</t>
         </is>
       </c>
       <c r="X25" t="n">

--- a/data/trending_integrated_20260910_10.xlsx
+++ b/data/trending_integrated_20260910_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+154.00%</t>
+          <t>+151.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F2" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>512072155908</v>
+        <v>519582707348</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NH스팩34호 합병 대상 신재생에너지 관련 기대감. 장 안좋을 때 수급 쏠림.</t>
+          <t>신재생에너지 합병 대상 스팩주로 수급 집중. 장세 불안 속 단기 급등 및 6천원 목표 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생에너지', '합병']</t>
+          <t>['스팩주', '신재생에너지', '단기 급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15710</v>
+        <v>241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+63.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>303</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12090</v>
+        <v>147</v>
       </c>
       <c r="K3" t="n">
-        <v>12730</v>
+        <v>181</v>
       </c>
       <c r="L3" t="n">
-        <v>15710</v>
+        <v>260</v>
       </c>
       <c r="M3" t="n">
-        <v>12720</v>
+        <v>181</v>
       </c>
       <c r="N3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>396257983</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3660</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>133</v>
+      </c>
+      <c r="R3" t="n">
         <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>223127221700</v>
-      </c>
-      <c r="P3" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R3" t="n">
-        <v>39000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흥구석유 유가 급등 수혜 기대. 이란 사태 및 지정학적 리스크 부각.</t>
+          <t>거래량 급증 및 2배 상승 기록, 회생 기대감 확산. 정매 대장주로서 추격 매수 및 상폐 우려 속 강세 지속.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가', '지정학적 리스크', '이란']</t>
+          <t>['거래량 급증', '회생 기대', '정매 대장주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>006380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14800</v>
+        <v>15470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+28.14%</t>
+          <t>+27.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>247</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>307</v>
       </c>
       <c r="H4" t="n">
-        <v>4.37</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11550</v>
+        <v>12090</v>
       </c>
       <c r="K4" t="n">
-        <v>11780</v>
+        <v>12730</v>
       </c>
       <c r="L4" t="n">
-        <v>14880</v>
+        <v>15710</v>
       </c>
       <c r="M4" t="n">
-        <v>11700</v>
+        <v>12720</v>
       </c>
       <c r="N4" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>71969624700</v>
+        <v>235204509775</v>
       </c>
       <c r="P4" t="n">
-        <v>33575</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>9690</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>12000</v>
+        <v>39000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 시세 분출. 뉴스 기반 단기 급등 전망.</t>
+          <t>트럼프 정책 및 중동 긴장 고조에 따른 유가 급등 기대. 실적 개선 가능성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['키 맞추기', '뉴스', '급등']</t>
+          <t>['유가', '브렌트유', '호르무즈']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28750</v>
+        <v>14390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+23.92%</t>
+          <t>+24.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>7.54</v>
+        <v>4.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23200</v>
+        <v>11550</v>
       </c>
       <c r="K5" t="n">
-        <v>26900</v>
+        <v>11780</v>
       </c>
       <c r="L5" t="n">
-        <v>30150</v>
+        <v>14880</v>
       </c>
       <c r="M5" t="n">
-        <v>24500</v>
+        <v>11700</v>
       </c>
       <c r="N5" t="n">
-        <v>7.58</v>
+        <v>4.63</v>
       </c>
       <c r="O5" t="n">
-        <v>32059977700</v>
+        <v>76027145275</v>
       </c>
       <c r="P5" t="n">
-        <v>34750</v>
+        <v>33575</v>
       </c>
       <c r="Q5" t="n">
-        <v>20450</v>
+        <v>9690</v>
       </c>
       <c r="R5" t="n">
-        <v>-37000</v>
+        <v>12000</v>
       </c>
       <c r="S5" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>샘표의 자사주 소각 가능성과 샘표식품과의 주주환원 정책 연계 기대감. 유동주식 대비 거래량 및 소각 필요성 언급.</t>
+          <t>흥구석유와의 키 맞추기 시세 분출 및 2연상 기대감 형성. 15% 이상 상승하며 테마주로서 강세 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 소각', '주주환원', 'PBR']</t>
+          <t>['키 맞추기', '시세 분출', '테마주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2155</v>
+        <v>28650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+22.44%</t>
+          <t>+23.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="H6" t="n">
-        <v>2.12</v>
+        <v>7.54</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1760</v>
+        <v>23200</v>
       </c>
       <c r="K6" t="n">
-        <v>1782</v>
+        <v>26900</v>
       </c>
       <c r="L6" t="n">
-        <v>2175</v>
+        <v>30150</v>
       </c>
       <c r="M6" t="n">
-        <v>1772</v>
+        <v>24500</v>
       </c>
       <c r="N6" t="n">
-        <v>2.07</v>
+        <v>7.58</v>
       </c>
       <c r="O6" t="n">
-        <v>119132420509</v>
+        <v>32899929475</v>
       </c>
       <c r="P6" t="n">
-        <v>4795</v>
+        <v>34750</v>
       </c>
       <c r="Q6" t="n">
-        <v>1524</v>
+        <v>20450</v>
       </c>
       <c r="R6" t="n">
-        <v>283000</v>
+        <v>-37000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 속 시세 형성 기대감. 단기 거래대금 증가 및 주가 상승.</t>
+          <t>샘표의 자사주 소각 가능성 및 주주환원 기대감과 함께 샘표식품의 주가 상승 및 PBR 개선 전망이 제기됩니다. 신한 외인 창구 매매 동향 및 높은 유보율에 대한 언급이 있습니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인', '시세', '거래량']</t>
+          <t>['자사주 소각', '주주환원', 'PBR']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3510</v>
+        <v>2080</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+13.04%</t>
+          <t>+18.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" t="n">
+        <v>41</v>
+      </c>
+      <c r="G7" t="n">
         <v>54</v>
       </c>
-      <c r="F7" t="n">
-        <v>33</v>
-      </c>
-      <c r="G7" t="n">
-        <v>32</v>
-      </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3105</v>
+        <v>1760</v>
       </c>
       <c r="K7" t="n">
-        <v>3170</v>
+        <v>1782</v>
       </c>
       <c r="L7" t="n">
-        <v>3775</v>
+        <v>2200</v>
       </c>
       <c r="M7" t="n">
-        <v>3165</v>
+        <v>1772</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O7" t="n">
-        <v>17614968186</v>
+        <v>137929328324</v>
       </c>
       <c r="P7" t="n">
-        <v>20800</v>
+        <v>4795</v>
       </c>
       <c r="Q7" t="n">
-        <v>1700</v>
+        <v>1524</v>
       </c>
       <c r="R7" t="n">
-        <v>16000</v>
+        <v>283000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>강한 수급 기반 상승세. 6천원 목표가 제시 및 단기 과열 구간 진입.</t>
+          <t>외국인 매수세 유입 속 단기 차익실현 및 물량 테스트 구간 진입. 상폐 위기 STX 대비 긍정적 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수급', '목표가', '단기과열']</t>
+          <t>['단기 차익', '물량 테스트', '상폐 위기']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8250</v>
+        <v>3535</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.19%</t>
+          <t>+13.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>913</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7420</v>
+        <v>3105</v>
       </c>
       <c r="K8" t="n">
-        <v>8000</v>
+        <v>3170</v>
       </c>
       <c r="L8" t="n">
-        <v>9100</v>
+        <v>3775</v>
       </c>
       <c r="M8" t="n">
-        <v>7930</v>
+        <v>3165</v>
       </c>
       <c r="N8" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>53292465300</v>
+        <v>18057831411</v>
       </c>
       <c r="P8" t="n">
-        <v>21500</v>
+        <v>20800</v>
       </c>
       <c r="Q8" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="R8" t="n">
-        <v>100000</v>
+        <v>16000</v>
       </c>
       <c r="S8" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>세계 폐암학회 참여 및 항암제 내성 극복 기술 기반 급등 기대. FDA 임상 2상 결과 및 기술 이전 주목.</t>
+          <t>강한 수급 기반 상승세. 6천원 목표가 제시 및 단기 과열 구간 진입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['폐암학회', '항암제', 'FDA']</t>
+          <t>['수급', '목표가', '단기과열']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3930</v>
+        <v>8320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+12.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.62</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>131</v>
+        <v>936</v>
       </c>
       <c r="H9" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3810</v>
+        <v>7420</v>
       </c>
       <c r="K9" t="n">
-        <v>3870</v>
+        <v>8000</v>
       </c>
       <c r="L9" t="n">
-        <v>4250</v>
+        <v>9100</v>
       </c>
       <c r="M9" t="n">
-        <v>3660</v>
+        <v>7930</v>
       </c>
       <c r="N9" t="n">
-        <v>3.19</v>
+        <v>0.77</v>
       </c>
       <c r="O9" t="n">
-        <v>109964602175</v>
+        <v>54438862200</v>
       </c>
       <c r="P9" t="n">
-        <v>8100</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>592</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>빛과전자 투기과열종목 회피 및 통신 관련 기술 기대감. 장기전 대비.</t>
+          <t>글로벌 제약사 참여 학회 및 항암제 내성 극복 연구 결과 기반 급등 기대. FDA 임상 2상 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['투기과열', '통신', '장기전']</t>
+          <t>['항암제', 'FDA', '오가노이드']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2125</v>
+        <v>544</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+7.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2085</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>2255</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>2395</v>
+        <v>585</v>
       </c>
       <c r="M10" t="n">
-        <v>2040</v>
+        <v>504</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>15410717850</v>
+        <v>6128209635</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>2610</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="R10" t="n">
-        <v>-4000</v>
+        <v>-205000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>새만금 소식 기반 긍정적 움직임. 외인 매수세 관찰 및 저항 구간 분석.</t>
+          <t>기업 병합 후 상장 가능성 언급되나, 상폐 및 거래 정지 관련 상반된 의견 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['새만금', '외인', '저항']</t>
+          <t>['병합', '상폐', '거래정지']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>153600</v>
+        <v>3885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>-1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>290</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>690</v>
+        <v>134</v>
       </c>
       <c r="H11" t="n">
-        <v>15.65</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>153500</v>
+        <v>3810</v>
       </c>
       <c r="K11" t="n">
-        <v>155500</v>
+        <v>3870</v>
       </c>
       <c r="L11" t="n">
-        <v>164700</v>
+        <v>4250</v>
       </c>
       <c r="M11" t="n">
-        <v>152500</v>
+        <v>3660</v>
       </c>
       <c r="N11" t="n">
-        <v>15.25</v>
+        <v>3.19</v>
       </c>
       <c r="O11" t="n">
-        <v>264886249900</v>
+        <v>112844924073</v>
       </c>
       <c r="P11" t="n">
-        <v>164700</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>87700</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>112000</v>
+        <v>20000</v>
       </c>
       <c r="S11" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK이노베이션 유가 급등 수혜 기대. 재무 개선 및 주주 이익 증대 전망.</t>
+          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['유가', '정제마진', '재무 개선']</t>
+          <t>['투경', '6G', '장기전']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>264250</v>
+        <v>2125</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>791</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>460</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>1251</v>
+        <v>157</v>
       </c>
       <c r="H12" t="n">
-        <v>46.81</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>269500</v>
+        <v>2085</v>
       </c>
       <c r="K12" t="n">
-        <v>269000</v>
+        <v>2255</v>
       </c>
       <c r="L12" t="n">
-        <v>270500</v>
+        <v>2395</v>
       </c>
       <c r="M12" t="n">
-        <v>263500</v>
+        <v>2040</v>
       </c>
       <c r="N12" t="n">
-        <v>46.85</v>
+        <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>1212617634500</v>
+        <v>16590302755</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>2930</v>
       </c>
       <c r="Q12" t="n">
-        <v>71600</v>
+        <v>910</v>
       </c>
       <c r="R12" t="n">
-        <v>236000</v>
+        <v>-4000</v>
       </c>
       <c r="S12" t="n">
-        <v>-272000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자 주가 하락에 대한 부정적 전망. 외인 매도 및 악재 요인 언급.</t>
+          <t>새만금 사업 및 외국인 매수세 유입에 따른 상승 기대감. 저가 매수 권유.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['악재', '외인 매도', '반도체']</t>
+          <t>['새만금', '매집', '외인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1816000</v>
+        <v>154000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>793</v>
+        <v>306</v>
       </c>
       <c r="F13" t="n">
-        <v>481</v>
+        <v>151</v>
       </c>
       <c r="G13" t="n">
-        <v>1306</v>
+        <v>720</v>
       </c>
       <c r="H13" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K13" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L13" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M13" t="n">
-        <v>1811000</v>
+        <v>152500</v>
       </c>
       <c r="N13" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2166983396000</v>
+        <v>273605438500</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q13" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R13" t="n">
-        <v>-64000</v>
+        <v>112000</v>
       </c>
       <c r="S13" t="n">
-        <v>-67000</v>
+        <v>-5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대규모 자사주 소각 예정. ADR 괴리율 및 마녀의 날 변동성 고려, 매수 기회 관점.</t>
+          <t>유가 폭등 및 정제마진 고공행진 속 소폭 상승. JP모건 대량 매수 패턴 관찰 및 전고점 돌파 시도.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주소각', 'ADR', '마녀의날']</t>
+          <t>['유가 폭등', '정제마진', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18790</v>
+        <v>1830000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.21</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>797</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>475</v>
       </c>
       <c r="G14" t="n">
-        <v>211</v>
+        <v>1344</v>
       </c>
       <c r="H14" t="n">
-        <v>10.64</v>
+        <v>50.67</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19450</v>
+        <v>1856000</v>
       </c>
       <c r="K14" t="n">
-        <v>18900</v>
+        <v>1879000</v>
       </c>
       <c r="L14" t="n">
-        <v>19220</v>
+        <v>1890000</v>
       </c>
       <c r="M14" t="n">
-        <v>18670</v>
+        <v>1811000</v>
       </c>
       <c r="N14" t="n">
-        <v>10.85</v>
+        <v>50.66</v>
       </c>
       <c r="O14" t="n">
-        <v>51867278060</v>
+        <v>2299079569000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>293000</v>
       </c>
       <c r="R14" t="n">
-        <v>58000</v>
+        <v>-64000</v>
       </c>
       <c r="S14" t="n">
-        <v>-29000</v>
+        <v>-67000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대우건설 주가 하락 및 불확실성. 중동전쟁 영향 미미 속 단기 반등 기대.</t>
+          <t>옵션 만기 및 리밸런싱 영향으로 변동성 확대. ADR 상승분 반락 및 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대우건설', '주가', '중동전쟁']</t>
+          <t>['옵션만기', 'ADR', '리밸런싱']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13820</v>
+        <v>264500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>791</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>460</v>
       </c>
       <c r="G15" t="n">
-        <v>269</v>
+        <v>1247</v>
       </c>
       <c r="H15" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14320</v>
+        <v>269500</v>
       </c>
       <c r="K15" t="n">
-        <v>13800</v>
+        <v>269000</v>
       </c>
       <c r="L15" t="n">
-        <v>13900</v>
+        <v>270500</v>
       </c>
       <c r="M15" t="n">
-        <v>13260</v>
+        <v>263500</v>
       </c>
       <c r="N15" t="n">
-        <v>5.64</v>
+        <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>67397865850</v>
+        <v>1289457575500</v>
       </c>
       <c r="P15" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3540</v>
+        <v>71600</v>
       </c>
       <c r="R15" t="n">
-        <v>-70000</v>
+        <v>236000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-272000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 소식 기반 상승 기대. 공매도 금지 지정 및 단기 조정 예상.</t>
+          <t>하이닉스 대비 상대적 약세 및 자사주 매입 관련 리스크 우려. 외인 매도세와 대규모 매도 발생으로 인한 하락세 지속.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '조정']</t>
+          <t>['자사주 매입', '외인 매도', '하락세']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29200</v>
+        <v>13850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.02</v>
+        <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33</v>
+        <v>6.09</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>30300</v>
+        <v>14320</v>
       </c>
       <c r="K16" t="n">
-        <v>30800</v>
+        <v>13800</v>
       </c>
       <c r="L16" t="n">
-        <v>31500</v>
+        <v>13900</v>
       </c>
       <c r="M16" t="n">
-        <v>27750</v>
+        <v>13260</v>
       </c>
       <c r="N16" t="n">
-        <v>0.31</v>
+        <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>88597288325</v>
+        <v>70513321450</v>
       </c>
       <c r="P16" t="n">
-        <v>39350</v>
+        <v>30200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8200</v>
+        <v>3540</v>
       </c>
       <c r="R16" t="n">
-        <v>-1000</v>
+        <v>-70000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>하락 추세 지속 및 매수세 실종으로 인한 부정적 전망. 축제는 끝났다는 의견. 단기적인 희망 회로를 경계.</t>
+          <t>미국 신규 원전 건설 소식 기반 상승 기대. 공매도 금지 지정 및 단기 조정 예상.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['계단식 하락', '매수세 실종', '신규주']</t>
+          <t>['원전', '공매도', '조정']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88100</v>
+        <v>18750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.93%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>644</v>
+        <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>91700</v>
+        <v>19450</v>
       </c>
       <c r="K17" t="n">
-        <v>90000</v>
+        <v>18900</v>
       </c>
       <c r="L17" t="n">
-        <v>90700</v>
+        <v>19220</v>
       </c>
       <c r="M17" t="n">
-        <v>87800</v>
+        <v>18670</v>
       </c>
       <c r="N17" t="n">
-        <v>23.61</v>
+        <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>100434741100</v>
+        <v>53354042360</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-73000</v>
+        <v>58000</v>
       </c>
       <c r="S17" t="n">
-        <v>-24000</v>
+        <v>-29000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
+          <t>미국 투자 및 원전 관련 긍정적 언급 속 차익실현 매물 출회. 미국 증시 영향으로 인한 단기 조정 국면 예상.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', '팀코리아', '웨스팅하우스']</t>
+          <t>['미국 투자', '원전', '차익실현']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14320</v>
+        <v>14420</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.28%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.34</v>
       </c>
       <c r="E18" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H18" t="n">
         <v>2.89</v>
@@ -2082,7 +2082,7 @@
         <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>66636849750</v>
+        <v>68012383295</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6560</v>
+        <v>88200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.03</v>
+        <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="G19" t="n">
-        <v>177</v>
+        <v>660</v>
       </c>
       <c r="H19" t="n">
-        <v>15.68</v>
+        <v>23.65</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6860</v>
+        <v>91700</v>
       </c>
       <c r="K19" t="n">
-        <v>6800</v>
+        <v>90000</v>
       </c>
       <c r="L19" t="n">
-        <v>6820</v>
+        <v>90700</v>
       </c>
       <c r="M19" t="n">
-        <v>6400</v>
+        <v>87800</v>
       </c>
       <c r="N19" t="n">
-        <v>16.71</v>
+        <v>23.61</v>
       </c>
       <c r="O19" t="n">
-        <v>8046225795</v>
+        <v>104972935050</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-131000</v>
+        <v>-73000</v>
       </c>
       <c r="S19" t="n">
-        <v>-4000</v>
+        <v>-24000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 잡주 이미지 형성. 분사 및 경영진 교체 요구.</t>
+          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국인', '분사', '경영진']</t>
+          <t>['원전', '팀코리아', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12370</v>
+        <v>14950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="H20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13030</v>
+        <v>15640</v>
       </c>
       <c r="K20" t="n">
-        <v>13160</v>
+        <v>15600</v>
       </c>
       <c r="L20" t="n">
-        <v>13240</v>
+        <v>15600</v>
       </c>
       <c r="M20" t="n">
-        <v>12150</v>
+        <v>14700</v>
       </c>
       <c r="N20" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>49128063860</v>
+        <v>17630560050</v>
       </c>
       <c r="P20" t="n">
-        <v>20850</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>4020</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>231000</v>
+        <v>-14000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
+          <t>건설업 흑자 전환 및 반도체 설계 용역 발주 소식에도 불구하고 하락세 지속. 투매 및 개별 종목 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호재', '원전', '하락']</t>
+          <t>['건설', '반도체', '투매']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14800</v>
+        <v>6530</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-5.37%</t>
+          <t>-4.81%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>244</v>
+        <v>190</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>15.68</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15640</v>
+        <v>6860</v>
       </c>
       <c r="K21" t="n">
-        <v>15600</v>
+        <v>6800</v>
       </c>
       <c r="L21" t="n">
-        <v>15600</v>
+        <v>6820</v>
       </c>
       <c r="M21" t="n">
-        <v>14700</v>
+        <v>6400</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>16.71</v>
       </c>
       <c r="O21" t="n">
-        <v>16794377895</v>
+        <v>8198047325</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>13000</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>6030</v>
       </c>
       <c r="R21" t="n">
-        <v>-14000</v>
+        <v>-131000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>호남 반도체 설계 용역 발주 및 건설 흑자 기반 상승 기대. 14000원 목표가 제시.</t>
+          <t>외국인 매도세 및 잡주 논란 속 하락세. 분사 이슈 및 로봇/반도체 사업 기대감에도 불구하고 부정적 투자 심리 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체', '건설', '흑자']</t>
+          <t>['외국인 매도', '분사 이슈', '투자 심리']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3620</v>
+        <v>12400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-6.34%</t>
+          <t>-4.83%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.54</v>
+        <v>-0.22</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="H22" t="n">
-        <v>1.54</v>
+        <v>0.14</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3865</v>
+        <v>13030</v>
       </c>
       <c r="K22" t="n">
-        <v>3845</v>
+        <v>13160</v>
       </c>
       <c r="L22" t="n">
-        <v>4075</v>
+        <v>13240</v>
       </c>
       <c r="M22" t="n">
-        <v>3605</v>
+        <v>12150</v>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>40602477592</v>
+        <v>49778308235</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>20850</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>4020</v>
       </c>
       <c r="R22" t="n">
-        <v>-73000</v>
+        <v>231000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 조정 예상 속 단기 매매 관점. 차트 분석 기반으로 방향성 제시.</t>
+          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['차트', '매수', '단타']</t>
+          <t>['호재', '원전', '하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-6.42%</t>
+          <t>-6.19%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H23" t="n">
         <v>4.91</v>
@@ -2542,7 +2542,7 @@
         <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>4102132365</v>
+        <v>4163131340</v>
       </c>
       <c r="P23" t="n">
         <v>2705</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>써니전자 경영권 분쟁 및 M&amp;A 관련 기대감. 새로운 대주주 관련 언급.</t>
+          <t>적대적 M&amp;A 가능성 및 신규 대주주 등장으로 인한 변동성 확대. 1만원 목표 제시 및 경영권 분쟁 관련 이슈 부각.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '경영권', '대주주']</t>
+          <t>['M&amp;A', '신규 대주주', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28950</v>
+        <v>3625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-6.21%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>-0.54</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="H24" t="n">
-        <v>12.31</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31100</v>
+        <v>3865</v>
       </c>
       <c r="K24" t="n">
-        <v>30450</v>
+        <v>3845</v>
       </c>
       <c r="L24" t="n">
-        <v>30600</v>
+        <v>4075</v>
       </c>
       <c r="M24" t="n">
-        <v>28800</v>
+        <v>3605</v>
       </c>
       <c r="N24" t="n">
-        <v>12.14</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>38872418800</v>
+        <v>41173859601</v>
       </c>
       <c r="P24" t="n">
-        <v>75900</v>
+        <v>4335</v>
       </c>
       <c r="Q24" t="n">
-        <v>15000</v>
+        <v>1246</v>
       </c>
       <c r="R24" t="n">
-        <v>-198000</v>
+        <v>-73000</v>
       </c>
       <c r="S24" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>대한전선 주가 변동성 확대. 상승분 반납 및 단기 하락세 우세.</t>
+          <t>주가 조정 및 하락 전망이 우세하나, 일부 단기 상승 및 분할 매수 의견 존재.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['변동성', '주가', '상승분 반납']</t>
+          <t>['조정', '분할 매수', '나락']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>144</v>
+        <v>28350</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-41.94%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.32</v>
+        <v>0.02</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="H25" t="n">
-        <v>5.86</v>
+        <v>0.33</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,38 +2711,38 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>248</v>
+        <v>30300</v>
       </c>
       <c r="K25" t="n">
-        <v>172</v>
+        <v>30800</v>
       </c>
       <c r="L25" t="n">
-        <v>172</v>
+        <v>31500</v>
       </c>
       <c r="M25" t="n">
-        <v>137</v>
+        <v>27750</v>
       </c>
       <c r="N25" t="n">
-        <v>6.18</v>
+        <v>0.31</v>
       </c>
       <c r="O25" t="n">
-        <v>567452546</v>
+        <v>95699601875</v>
       </c>
       <c r="P25" t="n">
-        <v>901</v>
+        <v>39350</v>
       </c>
       <c r="Q25" t="n">
-        <v>137</v>
+        <v>8200</v>
       </c>
       <c r="R25" t="n">
-        <v>29000</v>
+        <v>-1000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>시가총액 미달 상폐 우려 속 급락. 허매수/허매도 관찰 및 거래 정지 가능성 제기.</t>
+          <t>계단식 하락 추세 및 매수세 실종. 희망회로 걷어내고 손절 권유.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,18 +2751,202 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['상폐', '시가총액', '거래정지']</t>
+          <t>['계단식 하락', '매수세 실종', '손절']</t>
         </is>
       </c>
       <c r="X25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-6.59%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E26" t="n">
+        <v>55</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" t="n">
+        <v>93</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>31100</v>
+      </c>
+      <c r="K26" t="n">
+        <v>30450</v>
+      </c>
+      <c r="L26" t="n">
+        <v>30600</v>
+      </c>
+      <c r="M26" t="n">
+        <v>28800</v>
+      </c>
+      <c r="N26" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="O26" t="n">
+        <v>40091862525</v>
+      </c>
+      <c r="P26" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-198000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>전일 상승분 반납 및 차익실현 매물 출회. 시간당 매도 물량 증가하며 하락세 전환 가능성 시사.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>['차익실현', '매도 물량', '하락세']</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>144</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-41.94%</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>61</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>248</v>
+      </c>
+      <c r="K27" t="n">
+        <v>172</v>
+      </c>
+      <c r="L27" t="n">
+        <v>172</v>
+      </c>
+      <c r="M27" t="n">
+        <v>137</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O27" t="n">
+        <v>567452546</v>
+      </c>
+      <c r="P27" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>137</v>
+      </c>
+      <c r="R27" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>시가총액 미달 상폐 우려 및 급격한 하락세. 텐버거 종목 언급은 허위 기대.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>['상폐', '시총미달', '허매수']</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>008290</t>
         </is>

--- a/data/trending_integrated_20260910_10.xlsx
+++ b/data/trending_integrated_20260910_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5020</v>
+        <v>5045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+151.00%</t>
+          <t>+152.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>519582707348</v>
+        <v>527288039773</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신재생에너지 합병 대상 스팩주로 수급 집중. 장세 불안 속 단기 급등 및 6천원 목표 제시.</t>
+          <t>합병 대상 신재생에너지 업종 주목 속 스팩주 급등. 150% 이상 상승하며 단기 차익 시현.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '신재생에너지', '단기 급등']</t>
+          <t>['스팩주', '신재생에너지', '단기차익']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -673,10 +673,10 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>거래량 급증 및 2배 상승 기록, 회생 기대감 확산. 정매 대장주로서 추격 매수 및 상폐 우려 속 강세 지속.</t>
+          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['거래량 급증', '회생 기대', '정매 대장주']</t>
+          <t>['급등', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15470</v>
+        <v>15380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+27.96%</t>
+          <t>+27.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="F4" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G4" t="n">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="H4" t="n">
         <v>0.03</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>235204509775</v>
+        <v>243715551300</v>
       </c>
       <c r="P4" t="n">
         <v>36200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>트럼프 정책 및 중동 긴장 고조에 따른 유가 급등 기대. 실적 개선 가능성.</t>
+          <t>유가 급등 및 지정학적 긴장 고조 속에서 상승 기대감 표출. 일부 투자자 매수세 유입 및 목표가 상향 의견.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '브렌트유', '호르무즈']</t>
+          <t>['유가', '호르무즈', '매집']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14390</v>
+        <v>14190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+24.59%</t>
+          <t>+22.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n">
         <v>4.37</v>
@@ -886,7 +886,7 @@
         <v>4.63</v>
       </c>
       <c r="O5" t="n">
-        <v>76027145275</v>
+        <v>79887942330</v>
       </c>
       <c r="P5" t="n">
         <v>33575</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>흥구석유와의 키 맞추기 시세 분출 및 2연상 기대감 형성. 15% 이상 상승하며 테마주로서 강세 전망.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['키 맞추기', '시세 분출', '테마주']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28650</v>
+        <v>27900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+23.49%</t>
+          <t>+20.26%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H6" t="n">
         <v>7.54</v>
@@ -978,7 +978,7 @@
         <v>7.58</v>
       </c>
       <c r="O6" t="n">
-        <v>32899929475</v>
+        <v>33833880750</v>
       </c>
       <c r="P6" t="n">
         <v>34750</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>샘표의 자사주 소각 가능성 및 주주환원 기대감과 함께 샘표식품의 주가 상승 및 PBR 개선 전망이 제기됩니다. 신한 외인 창구 매매 동향 및 높은 유보율에 대한 언급이 있습니다.</t>
+          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 소각', '주주환원', 'PBR']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2080</v>
+        <v>2050</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.18%</t>
+          <t>+16.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
         <v>2.12</v>
@@ -1070,7 +1070,7 @@
         <v>2.07</v>
       </c>
       <c r="O7" t="n">
-        <v>137929328324</v>
+        <v>149019500487</v>
       </c>
       <c r="P7" t="n">
         <v>4795</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 속 단기 차익실현 및 물량 테스트 구간 진입. 상폐 위기 STX 대비 긍정적 언급.</t>
+          <t>외인 매수세 유입 속 단기 차익실현 매물 출회. 120일선 돌파 기대감과 함께 단타 거래 성행.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기 차익', '물량 테스트', '상폐 위기']</t>
+          <t>['단타', '외인매수', '120일선']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3535</v>
+        <v>8240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.85%</t>
+          <t>+11.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="G8" t="n">
-        <v>39</v>
+        <v>972</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3105</v>
+        <v>7420</v>
       </c>
       <c r="K8" t="n">
-        <v>3170</v>
+        <v>8000</v>
       </c>
       <c r="L8" t="n">
-        <v>3775</v>
+        <v>9100</v>
       </c>
       <c r="M8" t="n">
-        <v>3165</v>
+        <v>7930</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>18057831411</v>
+        <v>55048846120</v>
       </c>
       <c r="P8" t="n">
-        <v>20800</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>16000</v>
+        <v>100000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>강한 수급 기반 상승세. 6천원 목표가 제시 및 단기 과열 구간 진입.</t>
+          <t>글로벌 제약사 참여 학회 및 항암제 내성 극복 연구 결과 기반 급등 기대. FDA 임상 2상 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수급', '목표가', '단기과열']</t>
+          <t>['항암제', 'FDA', '오가노이드']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8320</v>
+        <v>3435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+12.13%</t>
+          <t>+10.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>184</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>936</v>
+        <v>39</v>
       </c>
       <c r="H9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7420</v>
+        <v>3105</v>
       </c>
       <c r="K9" t="n">
-        <v>8000</v>
+        <v>3170</v>
       </c>
       <c r="L9" t="n">
-        <v>9100</v>
+        <v>3775</v>
       </c>
       <c r="M9" t="n">
-        <v>7930</v>
+        <v>3165</v>
       </c>
       <c r="N9" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>54438862200</v>
+        <v>18469418522</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>20800</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="R9" t="n">
-        <v>100000</v>
+        <v>16000</v>
       </c>
       <c r="S9" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>글로벌 제약사 참여 학회 및 항암제 내성 극복 연구 결과 기반 급등 기대. FDA 임상 2상 긍정적 전망.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항암제', 'FDA', '오가노이드']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+7.09%</t>
+          <t>+5.71%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
         <v>2.8</v>
@@ -1346,7 +1346,7 @@
         <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>6128209635</v>
+        <v>6335546943</v>
       </c>
       <c r="P10" t="n">
         <v>2610</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기업 병합 후 상장 가능성 언급되나, 상폐 및 거래 정지 관련 상반된 의견 혼재.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['병합', '상폐', '거래정지']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3885</v>
+        <v>2145</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.97%</t>
+          <t>+2.88%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.62</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="H11" t="n">
-        <v>1.57</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3810</v>
+        <v>2085</v>
       </c>
       <c r="K11" t="n">
-        <v>3870</v>
+        <v>2255</v>
       </c>
       <c r="L11" t="n">
-        <v>4250</v>
+        <v>2395</v>
       </c>
       <c r="M11" t="n">
-        <v>3660</v>
+        <v>2040</v>
       </c>
       <c r="N11" t="n">
-        <v>3.19</v>
+        <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>112844924073</v>
+        <v>16817068812</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>20000</v>
+        <v>-4000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
+          <t>외인 매수세 유입 및 새만금 관련 소식 언급. 매집 중이라는 의견과 함께 종목 흐름에 대한 관망세.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['투경', '6G', '장기전']</t>
+          <t>['매집', '외인', '새만금']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2125</v>
+        <v>3860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K12" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L12" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M12" t="n">
-        <v>2040</v>
+        <v>3660</v>
       </c>
       <c r="N12" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O12" t="n">
-        <v>16590302755</v>
+        <v>114439873211</v>
       </c>
       <c r="P12" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-4000</v>
+        <v>20000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>새만금 사업 및 외국인 매수세 유입에 따른 상승 기대감. 저가 매수 권유.</t>
+          <t>기술적 분석 기반 투경 회피 및 장기 상승 전망. 6G 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['새만금', '매집', '외인']</t>
+          <t>['투경', '6G', '장기전']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>154000</v>
+        <v>153800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F13" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G13" t="n">
-        <v>720</v>
+        <v>742</v>
       </c>
       <c r="H13" t="n">
         <v>15.65</v>
@@ -1622,7 +1622,7 @@
         <v>15.25</v>
       </c>
       <c r="O13" t="n">
-        <v>273605438500</v>
+        <v>279612063000</v>
       </c>
       <c r="P13" t="n">
         <v>164700</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 폭등 및 정제마진 고공행진 속 소폭 상승. JP모건 대량 매수 패턴 관찰 및 전고점 돌파 시도.</t>
+          <t>유가 폭등 및 정제마진 호조 속 강보합 마감. 전고점 돌파 기대감과 장기 보유 의견 상존.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가 폭등', '정제마진', '전고점 돌파']</t>
+          <t>['유가폭등', '정제마진', '전고점']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1830000</v>
+        <v>1832000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="F14" t="n">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G14" t="n">
-        <v>1344</v>
+        <v>1361</v>
       </c>
       <c r="H14" t="n">
         <v>50.67</v>
@@ -1714,7 +1714,7 @@
         <v>50.66</v>
       </c>
       <c r="O14" t="n">
-        <v>2299079569000</v>
+        <v>2452882101500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>옵션 만기 및 리밸런싱 영향으로 변동성 확대. ADR 상승분 반락 및 하락 우려.</t>
+          <t>ADR 상승에도 불구하고 국내 증시 약세 속 하락 마감. 옵션 만기일 영향 및 패닉셀 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['옵션만기', 'ADR', '리밸런싱']</t>
+          <t>['ADR', '옵션만기', '패닉셀']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264500</v>
+        <v>14070</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.45</v>
       </c>
       <c r="E15" t="n">
-        <v>791</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>460</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>1247</v>
+        <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>46.81</v>
+        <v>6.09</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>269500</v>
+        <v>14320</v>
       </c>
       <c r="K15" t="n">
-        <v>269000</v>
+        <v>13800</v>
       </c>
       <c r="L15" t="n">
-        <v>270500</v>
+        <v>14090</v>
       </c>
       <c r="M15" t="n">
-        <v>263500</v>
+        <v>13260</v>
       </c>
       <c r="N15" t="n">
-        <v>46.85</v>
+        <v>5.64</v>
       </c>
       <c r="O15" t="n">
-        <v>1289457575500</v>
+        <v>76223433030</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>30200</v>
       </c>
       <c r="Q15" t="n">
-        <v>71600</v>
+        <v>3540</v>
       </c>
       <c r="R15" t="n">
-        <v>236000</v>
+        <v>-70000</v>
       </c>
       <c r="S15" t="n">
-        <v>-272000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>하이닉스 대비 상대적 약세 및 자사주 매입 관련 리스크 우려. 외인 매도세와 대규모 매도 발생으로 인한 하락세 지속.</t>
+          <t>미국 신규 원전 건설 관련 호재 언급. 주포의 움직임 및 공매도 금지에 대한 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외인 매도', '하락세']</t>
+          <t>['원전', '공매도', '주포']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13850</v>
+        <v>264500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>789</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>456</v>
       </c>
       <c r="G16" t="n">
-        <v>275</v>
+        <v>1241</v>
       </c>
       <c r="H16" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14320</v>
+        <v>269500</v>
       </c>
       <c r="K16" t="n">
-        <v>13800</v>
+        <v>269000</v>
       </c>
       <c r="L16" t="n">
-        <v>13900</v>
+        <v>270500</v>
       </c>
       <c r="M16" t="n">
-        <v>13260</v>
+        <v>263500</v>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>46.85</v>
       </c>
       <c r="O16" t="n">
-        <v>70513321450</v>
+        <v>1401681724250</v>
       </c>
       <c r="P16" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>3540</v>
+        <v>71600</v>
       </c>
       <c r="R16" t="n">
-        <v>-70000</v>
+        <v>236000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-272000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 소식 기반 상승 기대. 공매도 금지 지정 및 단기 조정 예상.</t>
+          <t>반도체 섹터 약세 및 자사주 매입 리스크 언급. 외인 매도 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '조정']</t>
+          <t>['반도체', '자사주매입', '외인매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18750</v>
+        <v>18830</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>53354042360</v>
+        <v>55743498150</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 투자 및 원전 관련 긍정적 언급 속 차익실현 매물 출회. 미국 증시 영향으로 인한 단기 조정 국면 예상.</t>
+          <t>미국 투자 관련 긍정적 기대감 속 급락 마감. 중동전쟁 악재 영향 없다는 의견과 하락 전망 혼재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국 투자', '원전', '차익실현']</t>
+          <t>['미국투자', '중동전쟁', '급락']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14420</v>
+        <v>14460</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.61%</t>
+          <t>-3.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.34</v>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="H18" t="n">
         <v>2.89</v>
@@ -2082,7 +2082,7 @@
         <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>68012383295</v>
+        <v>69330301365</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 강세 및 AI 관련주 비교. 16000원 돌파 목표 및 시간 외 거래량 주목.</t>
+          <t>미국 광통신 관련주 강세 및 AI 관련주 언급. 외인 매수세 유입과 함께 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '시간외거래']</t>
+          <t>['광통신', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88200</v>
+        <v>88500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>-3.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G19" t="n">
-        <v>660</v>
+        <v>684</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2174,7 +2174,7 @@
         <v>23.61</v>
       </c>
       <c r="O19" t="n">
-        <v>104972935050</v>
+        <v>108082951500</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 신규 원전 8기 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성. 역사상 최대 호재.</t>
+          <t>미국 원전 건설 관련 초대형 호재 및 팀코리아 언급. 웨스턴하우스 인수전 참여 가능성 및 목표가 상향 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '팀코리아', '웨스팅하우스']</t>
+          <t>['원전', '웨스팅하우스', '호재']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,70 +2219,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14950</v>
+        <v>12460</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15640</v>
+        <v>13030</v>
       </c>
       <c r="K20" t="n">
-        <v>15600</v>
+        <v>13160</v>
       </c>
       <c r="L20" t="n">
-        <v>15600</v>
+        <v>13240</v>
       </c>
       <c r="M20" t="n">
-        <v>14700</v>
+        <v>12150</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="O20" t="n">
-        <v>17630560050</v>
+        <v>52306312645</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>20850</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>4020</v>
       </c>
       <c r="R20" t="n">
-        <v>-14000</v>
+        <v>231000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>건설업 흑자 전환 및 반도체 설계 용역 발주 소식에도 불구하고 하락세 지속. 투매 및 개별 종목 언급.</t>
+          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['건설', '반도체', '투매']</t>
+          <t>['호재', '원전', '하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6530</v>
+        <v>14920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-4.60%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="H21" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K21" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L21" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M21" t="n">
-        <v>6400</v>
+        <v>14700</v>
       </c>
       <c r="N21" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>8198047325</v>
+        <v>18016030775</v>
       </c>
       <c r="P21" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-131000</v>
+        <v>-14000</v>
       </c>
       <c r="S21" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 잡주 논란 속 하락세. 분사 이슈 및 로봇/반도체 사업 기대감에도 불구하고 부정적 투자 심리 지속.</t>
+          <t>건설업 흑자 전환 및 반도체 설계 용역 발주 소식에도 불구하고 하락세 지속. 투매 및 개별 종목 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외국인 매도', '분사 이슈', '투자 심리']</t>
+          <t>['건설', '반도체', '투매']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12400</v>
+        <v>6520</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.83%</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.22</v>
+        <v>-1.03</v>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v>15.68</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13030</v>
+        <v>6860</v>
       </c>
       <c r="K22" t="n">
-        <v>13160</v>
+        <v>6800</v>
       </c>
       <c r="L22" t="n">
-        <v>13240</v>
+        <v>6820</v>
       </c>
       <c r="M22" t="n">
-        <v>12150</v>
+        <v>6400</v>
       </c>
       <c r="N22" t="n">
-        <v>0.36</v>
+        <v>16.71</v>
       </c>
       <c r="O22" t="n">
-        <v>49778308235</v>
+        <v>8436678140</v>
       </c>
       <c r="P22" t="n">
-        <v>20850</v>
+        <v>13000</v>
       </c>
       <c r="Q22" t="n">
-        <v>4020</v>
+        <v>6030</v>
       </c>
       <c r="R22" t="n">
-        <v>231000</v>
+        <v>-131000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 기대 속 원전 테마 하락. 3500억 달러 규모 투자 및 단기 하락세 관찰.</t>
+          <t>외인 매도세 및 주가 패턴에 대한 불만 제기. 자사주 소각 및 분사 이슈 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['호재', '원전', '하락']</t>
+          <t>['외인', '자사주', '분사']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2120</v>
+        <v>3635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-6.19%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K23" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L23" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M23" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>4163131340</v>
+        <v>41781902380</v>
       </c>
       <c r="P23" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q23" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R23" t="n">
-        <v>-47000</v>
+        <v>-73000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>적대적 M&amp;A 가능성 및 신규 대주주 등장으로 인한 변동성 확대. 1만원 목표 제시 및 경영권 분쟁 관련 이슈 부각.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '신규 대주주', '경영권 분쟁']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3625</v>
+        <v>29150</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-6.21%</t>
+          <t>-6.27%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>41173859601</v>
+        <v>42016935250</v>
       </c>
       <c r="P24" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
-        <v>-73000</v>
+        <v>-198000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>주가 조정 및 하락 전망이 우세하나, 일부 단기 상승 및 분할 매수 의견 존재.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['조정', '분할 매수', '나락']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2694,13 +2694,13 @@
         <v>0.02</v>
       </c>
       <c r="E25" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="H25" t="n">
         <v>0.33</v>
@@ -2726,7 +2726,7 @@
         <v>0.31</v>
       </c>
       <c r="O25" t="n">
-        <v>95699601875</v>
+        <v>98194053750</v>
       </c>
       <c r="P25" t="n">
         <v>39350</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>계단식 하락 추세 및 매수세 실종. 희망회로 걷어내고 손절 권유.</t>
+          <t>계단식 하락 및 저점 지속 하락에 대한 부정적 전망. 주포 이탈 및 신규주 하락 패턴 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['계단식 하락', '매수세 실종', '손절']</t>
+          <t>['계단식하락', '저점', '주포']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2771,31 +2771,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29050</v>
+        <v>2100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.59%</t>
+          <t>-7.08%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="E26" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="H26" t="n">
-        <v>12.31</v>
+        <v>4.91</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,47 +2803,47 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>31100</v>
+        <v>2260</v>
       </c>
       <c r="K26" t="n">
-        <v>30450</v>
+        <v>2250</v>
       </c>
       <c r="L26" t="n">
-        <v>30600</v>
+        <v>2290</v>
       </c>
       <c r="M26" t="n">
-        <v>28800</v>
+        <v>2080</v>
       </c>
       <c r="N26" t="n">
-        <v>12.14</v>
+        <v>5.26</v>
       </c>
       <c r="O26" t="n">
-        <v>40091862525</v>
+        <v>4325107655</v>
       </c>
       <c r="P26" t="n">
-        <v>75900</v>
+        <v>2705</v>
       </c>
       <c r="Q26" t="n">
-        <v>15000</v>
+        <v>1418</v>
       </c>
       <c r="R26" t="n">
-        <v>-198000</v>
+        <v>-47000</v>
       </c>
       <c r="S26" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>전일 상승분 반납 및 차익실현 매물 출회. 시간당 매도 물량 증가하며 하락세 전환 가능성 시사.</t>
+          <t>적대적 M&amp;A 가능성 속 최대주주 변경. 5% 이상 하락하며 변동성 확대.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['차익실현', '매도 물량', '하락세']</t>
+          <t>['M&amp;A', '최대주주', '변동성']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F27" t="n">
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>시가총액 미달 상폐 우려 및 급격한 하락세. 텐버거 종목 언급은 허위 기대.</t>
+          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['상폐', '시총미달', '허매수']</t>
+          <t>['상폐', '시가총액', '허매수']</t>
         </is>
       </c>
       <c r="X27" t="n">
